--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="89">
   <si>
     <t>Project</t>
   </si>
@@ -3239,6 +3239,9 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="E51" s="3" t="s">
         <v>54</v>
       </c>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="89">
   <si>
     <t>Project</t>
   </si>
@@ -3244,6 +3244,51 @@
       </c>
       <c r="E51" s="3" t="s">
         <v>54</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O51" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P51" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S51" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="88">
   <si>
     <t>Project</t>
   </si>
@@ -175,9 +175,6 @@
   </si>
   <si>
     <t>KEEVA</t>
-  </si>
-  <si>
-    <t>Eslam</t>
   </si>
   <si>
     <t>Setting</t>
@@ -321,15 +318,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -3238,59 +3232,6 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F51" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G51" s="1">
-        <v>50.0</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I51" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="J51" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="K51" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L51" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="M51" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N51" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O51" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="R51" s="1">
-        <v>24.0</v>
-      </c>
-      <c r="S51" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -3313,26 +3254,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -4354,66 +4295,66 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>71</v>
+      <c r="B8" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -4421,7 +4362,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -4429,15 +4370,15 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>74</v>
+      <c r="B11" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -4445,7 +4386,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -4453,15 +4394,15 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>77</v>
+      <c r="B14" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -4469,15 +4410,15 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>79</v>
+      <c r="B16" s="3" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -4485,23 +4426,23 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
@@ -4509,31 +4450,31 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>86</v>
+      <c r="B21" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="87">
   <si>
     <t>Project</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>25% DP &amp; 25% After 3 Months No Years</t>
-  </si>
-  <si>
-    <t>1,4</t>
   </si>
   <si>
     <t>RTM</t>
@@ -318,11 +315,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1185,8 +1185,8 @@
       <c r="B12" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>34</v>
+      <c r="D12" s="2">
+        <v>4.0</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>33</v>
@@ -1240,10 +1240,10 @@
     </row>
     <row r="13">
       <c r="B13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="1">
         <v>2.0</v>
@@ -1293,10 +1293,10 @@
     </row>
     <row r="14">
       <c r="B14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="1">
         <v>3.0</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="15">
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" s="1">
         <v>4.0</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="16">
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" s="1">
         <v>5.0</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="17">
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" s="1">
         <v>6.0</v>
@@ -1509,10 +1509,10 @@
     </row>
     <row r="18">
       <c r="B18" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F18" s="1">
         <v>7.0</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1">
         <v>8.0</v>
@@ -1617,10 +1617,10 @@
     </row>
     <row r="20">
       <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" s="1">
         <v>0.0</v>
@@ -1670,13 +1670,13 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F21" s="1">
         <v>0.0</v>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" s="1">
         <v>8.0</v>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1">
         <v>7.0</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24" s="1">
         <v>6.0</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1">
         <v>5.0</v>
@@ -1938,13 +1938,13 @@
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="2">
+        <v>50</v>
+      </c>
+      <c r="C26" s="3">
         <v>20000.0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F26" s="1">
         <v>0.0</v>
@@ -1994,13 +1994,13 @@
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="2">
+        <v>50</v>
+      </c>
+      <c r="C27" s="3">
         <v>20000.0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F27" s="1">
         <v>8.0</v>
@@ -2050,13 +2050,13 @@
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="2">
+        <v>50</v>
+      </c>
+      <c r="C28" s="3">
         <v>20000.0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F28" s="1">
         <v>7.0</v>
@@ -2106,13 +2106,13 @@
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="2">
+        <v>50</v>
+      </c>
+      <c r="C29" s="3">
         <v>20000.0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1">
         <v>6.0</v>
@@ -2162,13 +2162,13 @@
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="2">
+        <v>50</v>
+      </c>
+      <c r="C30" s="3">
         <v>20000.0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F30" s="1">
         <v>5.0</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>21</v>
@@ -2731,7 +2731,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>21</v>
@@ -3254,26 +3254,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -4295,66 +4295,66 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
+      <c r="B8" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -4362,7 +4362,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -4370,15 +4370,15 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>73</v>
+      <c r="B11" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -4386,7 +4386,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -4394,15 +4394,15 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>76</v>
+      <c r="B14" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -4410,15 +4410,15 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>78</v>
+      <c r="B16" s="4" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -4426,23 +4426,23 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
@@ -4450,31 +4450,31 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>85</v>
+      <c r="B21" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="88">
   <si>
     <t>Project</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>RTM</t>
+  </si>
+  <si>
+    <t>1,2</t>
   </si>
   <si>
     <t>10% DP over 2 years</t>
@@ -1242,8 +1245,11 @@
       <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D13" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1">
         <v>2.0</v>
@@ -1295,8 +1301,11 @@
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D14" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E14" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F14" s="1">
         <v>3.0</v>
@@ -1349,8 +1358,11 @@
       <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D15" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" s="1">
         <v>4.0</v>
@@ -1403,8 +1415,11 @@
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D16" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F16" s="1">
         <v>5.0</v>
@@ -1457,8 +1472,11 @@
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D17" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F17" s="1">
         <v>6.0</v>
@@ -1511,8 +1529,11 @@
       <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D18" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1">
         <v>7.0</v>
@@ -1565,8 +1586,11 @@
       <c r="B19" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D19" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" s="1">
         <v>8.0</v>
@@ -1619,8 +1643,11 @@
       <c r="B20" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="D20" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="E20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" s="1">
         <v>0.0</v>
@@ -1670,13 +1697,13 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F21" s="1">
         <v>0.0</v>
@@ -1726,10 +1753,10 @@
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1">
         <v>8.0</v>
@@ -1779,10 +1806,10 @@
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1">
         <v>7.0</v>
@@ -1832,10 +1859,10 @@
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F24" s="1">
         <v>6.0</v>
@@ -1885,10 +1912,10 @@
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F25" s="1">
         <v>5.0</v>
@@ -1938,13 +1965,13 @@
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C26" s="3">
         <v>20000.0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26" s="1">
         <v>0.0</v>
@@ -1994,13 +2021,13 @@
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C27" s="3">
         <v>20000.0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F27" s="1">
         <v>8.0</v>
@@ -2050,13 +2077,13 @@
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C28" s="3">
         <v>20000.0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F28" s="1">
         <v>7.0</v>
@@ -2106,13 +2133,13 @@
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C29" s="3">
         <v>20000.0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F29" s="1">
         <v>6.0</v>
@@ -2162,13 +2189,13 @@
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C30" s="3">
         <v>20000.0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F30" s="1">
         <v>5.0</v>
@@ -2218,7 +2245,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>21</v>
@@ -2731,7 +2758,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>21</v>
@@ -3254,26 +3281,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -4295,58 +4322,58 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -4354,7 +4381,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -4362,7 +4389,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -4370,7 +4397,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
@@ -4378,7 +4405,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -4386,7 +4413,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -4394,7 +4421,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -4402,7 +4429,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -4410,7 +4437,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -4418,7 +4445,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -4426,23 +4453,23 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
@@ -4450,7 +4477,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
@@ -4458,23 +4485,23 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="87">
   <si>
     <t>Project</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t>RTM</t>
-  </si>
-  <si>
-    <t>1,2</t>
   </si>
   <si>
     <t>10% DP over 2 years</t>
@@ -1245,11 +1242,8 @@
       <c r="B13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="F13" s="1">
         <v>2.0</v>
@@ -1301,11 +1295,8 @@
       <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="1">
         <v>3.0</v>
@@ -1358,11 +1349,8 @@
       <c r="B15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" s="1">
         <v>4.0</v>
@@ -1415,11 +1403,8 @@
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F16" s="1">
         <v>5.0</v>
@@ -1472,11 +1457,8 @@
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E17" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17" s="1">
         <v>6.0</v>
@@ -1529,11 +1511,8 @@
       <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F18" s="1">
         <v>7.0</v>
@@ -1586,11 +1565,8 @@
       <c r="B19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1">
         <v>8.0</v>
@@ -1643,11 +1619,8 @@
       <c r="B20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F20" s="1">
         <v>0.0</v>
@@ -1697,13 +1670,13 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="F21" s="1">
         <v>0.0</v>
@@ -1753,10 +1726,10 @@
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" s="1">
         <v>8.0</v>
@@ -1806,10 +1779,10 @@
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1">
         <v>7.0</v>
@@ -1859,10 +1832,10 @@
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F24" s="1">
         <v>6.0</v>
@@ -1912,10 +1885,10 @@
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F25" s="1">
         <v>5.0</v>
@@ -1965,13 +1938,13 @@
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="3">
         <v>20000.0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F26" s="1">
         <v>0.0</v>
@@ -2021,13 +1994,13 @@
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" s="3">
         <v>20000.0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F27" s="1">
         <v>8.0</v>
@@ -2077,13 +2050,13 @@
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" s="3">
         <v>20000.0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F28" s="1">
         <v>7.0</v>
@@ -2133,13 +2106,13 @@
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" s="3">
         <v>20000.0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1">
         <v>6.0</v>
@@ -2189,13 +2162,13 @@
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C30" s="3">
         <v>20000.0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F30" s="1">
         <v>5.0</v>
@@ -2245,7 +2218,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>21</v>
@@ -2758,7 +2731,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>21</v>
@@ -3281,26 +3254,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -4322,58 +4295,58 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -4381,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -4389,7 +4362,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -4397,7 +4370,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
@@ -4405,7 +4378,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -4413,7 +4386,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -4421,7 +4394,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -4429,7 +4402,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -4437,7 +4410,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -4445,7 +4418,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -4453,23 +4426,23 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
@@ -4477,7 +4450,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
@@ -4485,23 +4458,23 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -1168,11 +1168,11 @@
       <c r="P11" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R11" s="2">
         <v>18.0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>30.0</v>
       </c>
       <c r="S11" s="1">
         <v>6.0</v>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -75,7 +75,7 @@
     <t>YOUD</t>
   </si>
   <si>
-    <t>Primary</t>
+    <t>YOUD &amp; YOUD EL BAHR</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
@@ -637,7 +637,7 @@
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -692,7 +692,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -747,7 +747,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -802,7 +802,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -856,7 +856,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -910,7 +910,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -964,7 +964,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1018,7 +1018,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1072,7 +1072,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1126,7 +1126,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1182,7 +1182,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="2">

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="88">
   <si>
     <t>Project</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>KEEVA</t>
+  </si>
+  <si>
+    <t>GAIA</t>
   </si>
   <si>
     <t>Setting</t>
@@ -3232,6 +3235,389 @@
         <v>22</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L51" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M51" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N51" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O51" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="E52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K52" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L52" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="M52" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N52" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="O52" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T52" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="E53" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="J53" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K53" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L53" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O53" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="E54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F54" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I54" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J54" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K54" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L54" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O54" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="E55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I55" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="J55" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="K55" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L55" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O55" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="E56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="J56" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="K56" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L56" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M56" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N56" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O56" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="E57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="J57" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="K57" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L57" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M57" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N57" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O57" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="E58" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F58" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J58" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K58" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L58" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M58" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N58" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O58" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="E59" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F59" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="J59" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="K59" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L59" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M59" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N59" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O59" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="E60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O60" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -3254,26 +3640,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -4295,58 +4681,58 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -4354,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -4362,7 +4748,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -4370,7 +4756,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
@@ -4378,7 +4764,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -4386,7 +4772,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -4394,7 +4780,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -4402,7 +4788,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -4410,7 +4796,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -4418,7 +4804,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -4426,23 +4812,23 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
@@ -4450,7 +4836,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
@@ -4458,23 +4844,23 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -3273,7 +3273,7 @@
         <v>10.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -3311,7 +3311,7 @@
         <v>10.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -3349,7 +3349,7 @@
         <v>10.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -3387,7 +3387,7 @@
         <v>10.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -3425,7 +3425,7 @@
         <v>10.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -3463,7 +3463,7 @@
         <v>10.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -3501,7 +3501,7 @@
         <v>10.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -3539,7 +3539,7 @@
         <v>10.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
@@ -3577,7 +3577,7 @@
         <v>10.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -3615,7 +3615,7 @@
         <v>10.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="96">
   <si>
     <t>Project</t>
   </si>
@@ -142,6 +142,30 @@
   </si>
   <si>
     <t>Cash discount 15%</t>
+  </si>
+  <si>
+    <t>Delivery 1 Year</t>
+  </si>
+  <si>
+    <t>10% DP over 4 years</t>
+  </si>
+  <si>
+    <t>7.5% DP &amp; 7.5% After 3 months over 5 years</t>
+  </si>
+  <si>
+    <t>10% DP &amp; 10% After 3 months over 6 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5% DP &amp; 12.5% After 3 months over 7 years </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15% DP &amp; 15% After 3 months over 8 years </t>
+  </si>
+  <si>
+    <t>17.5% DP &amp; 17.5% After 3 months over 9 years</t>
+  </si>
+  <si>
+    <t>20% DP &amp; 20% After 3 months over 10 years</t>
   </si>
   <si>
     <t>The Mornings_Everyday</t>
@@ -1672,477 +1696,466 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="G21" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J21" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="1">
+        <f>4*4</f>
+        <v>16</v>
+      </c>
+      <c r="M21" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N21" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O21" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P21" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R21" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S21" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="H21" s="1" t="s">
+      <c r="F22" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="J22" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="K22" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N22" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O22" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P22" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R22" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I21" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q21" s="1">
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="K23" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L23" s="2">
+        <v>23.0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N23" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O23" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P23" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R23" s="2">
         <v>15.0</v>
       </c>
-      <c r="R21" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="1">
+      <c r="S23" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="G24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="J24" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="K24" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>27.0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O24" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P24" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R24" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="S24" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="2">
         <v>8.0</v>
       </c>
-      <c r="G22" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L22" s="1">
+      <c r="G25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L25" s="2">
         <v>31.0</v>
       </c>
-      <c r="M22" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N22" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O22" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P22" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q22" s="1">
+      <c r="M25" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O25" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P25" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R25" s="2">
         <v>15.0</v>
       </c>
-      <c r="R22" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q23" s="1">
+      <c r="S25" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="J26" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="K26" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="M26" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O26" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P26" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R26" s="2">
         <v>15.0</v>
       </c>
-      <c r="R23" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S23" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L24" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N24" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O24" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P24" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q24" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R24" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S24" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O25" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R25" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S25" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="3">
-        <v>20000.0</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="O26" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P26" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R26" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S26" s="1">
-        <v>6.0</v>
+      <c r="S26" s="2">
+        <v>3.0</v>
       </c>
       <c r="T26" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="3">
-        <v>20000.0</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F27" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="G27" s="1">
+      <c r="F27" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G27" s="2">
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N27" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O27" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P27" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q27" s="1">
+        <v>22</v>
+      </c>
+      <c r="I27" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>39.0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O27" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P27" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R27" s="2">
         <v>15.0</v>
       </c>
-      <c r="R27" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S27" s="1">
-        <v>6.0</v>
+      <c r="S27" s="2">
+        <v>3.0</v>
       </c>
       <c r="T27" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="3">
-        <v>20000.0</v>
+      <c r="B28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="G28" s="1">
-        <v>3.0</v>
+        <v>42</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="2">
+        <v>15.0</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I28" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J28" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K28" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L28" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N28" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O28" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P28" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q28" s="1">
+      <c r="I28" s="2">
+        <v>100.0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P28" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="Q28" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R28" s="2">
         <v>15.0</v>
       </c>
-      <c r="R28" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S28" s="1">
-        <v>6.0</v>
+      <c r="S28" s="2">
+        <v>3.0</v>
       </c>
       <c r="T28" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="B29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="3">
-        <v>20000.0</v>
+        <v>52</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F29" s="1">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="G29" s="1">
-        <v>6.0</v>
+        <v>25.0</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="I29" s="1">
-        <v>5.0</v>
+        <v>100.0</v>
       </c>
       <c r="J29" s="1">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="K29" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L29" s="1">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="M29" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N29" s="1">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="O29" s="1">
         <v>10.0</v>
@@ -2160,27 +2173,24 @@
         <v>6.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="3">
-        <v>20000.0</v>
+        <v>52</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F30" s="1">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G30" s="1">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I30" s="1">
         <v>5.0</v>
@@ -2216,21 +2226,21 @@
         <v>6.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>51</v>
+      <c r="B31" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="F31" s="1">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G31" s="1">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>22</v>
@@ -2257,14 +2267,13 @@
         <v>10.0</v>
       </c>
       <c r="P31" s="1">
-        <f t="shared" ref="P31:P40" si="3">4*12</f>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q31" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R31" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S31" s="1">
         <v>6.0</v>
@@ -2274,48 +2283,50 @@
       </c>
     </row>
     <row r="32">
+      <c r="B32" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="E32" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F32" s="1">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G32" s="1">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I32" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="J32" s="1">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K32" s="1">
         <v>3.0</v>
       </c>
       <c r="L32" s="1">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="M32" s="1">
         <v>3.0</v>
       </c>
       <c r="N32" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="O32" s="1">
         <v>10.0</v>
       </c>
       <c r="P32" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q32" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R32" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S32" s="1">
         <v>6.0</v>
@@ -2325,23 +2336,26 @@
       </c>
     </row>
     <row r="33">
+      <c r="B33" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="E33" s="1" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F33" s="1">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G33" s="1">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I33" s="1">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="J33" s="1">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="K33" s="1">
         <v>3.0</v>
@@ -2359,14 +2373,13 @@
         <v>10.0</v>
       </c>
       <c r="P33" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q33" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R33" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S33" s="1">
         <v>6.0</v>
@@ -2376,74 +2389,85 @@
       </c>
     </row>
     <row r="34">
+      <c r="B34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="3">
+        <v>20000.0</v>
+      </c>
       <c r="E34" s="1" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="F34" s="1">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G34" s="1">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I34" s="1">
-        <v>10.0</v>
+        <v>100.0</v>
       </c>
       <c r="J34" s="1">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="K34" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L34" s="1">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="M34" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N34" s="1">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="O34" s="1">
         <v>10.0</v>
       </c>
       <c r="P34" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q34" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R34" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S34" s="1">
         <v>6.0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
+      <c r="B35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="3">
+        <v>20000.0</v>
+      </c>
       <c r="E35" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="F35" s="1">
         <v>8.0</v>
       </c>
       <c r="G35" s="1">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I35" s="1">
-        <v>12.5</v>
+        <v>5.0</v>
       </c>
       <c r="J35" s="1">
-        <v>12.5</v>
+        <v>5.0</v>
       </c>
       <c r="K35" s="1">
         <v>3.0</v>
@@ -2461,40 +2485,45 @@
         <v>10.0</v>
       </c>
       <c r="P35" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q35" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R35" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S35" s="1">
         <v>6.0</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
+      <c r="B36" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="3">
+        <v>20000.0</v>
+      </c>
       <c r="E36" s="1" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F36" s="1">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G36" s="1">
-        <v>30.0</v>
+        <v>3.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I36" s="1">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="J36" s="1">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="K36" s="1">
         <v>3.0</v>
@@ -2512,40 +2541,45 @@
         <v>10.0</v>
       </c>
       <c r="P36" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q36" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R36" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S36" s="1">
         <v>6.0</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
+      <c r="B37" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="3">
+        <v>20000.0</v>
+      </c>
       <c r="E37" s="1" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F37" s="1">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G37" s="1">
-        <v>35.0</v>
+        <v>6.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I37" s="1">
-        <v>17.5</v>
+        <v>5.0</v>
       </c>
       <c r="J37" s="1">
-        <v>17.5</v>
+        <v>5.0</v>
       </c>
       <c r="K37" s="1">
         <v>3.0</v>
@@ -2563,40 +2597,45 @@
         <v>10.0</v>
       </c>
       <c r="P37" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q37" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R37" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S37" s="1">
         <v>6.0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
+      <c r="B38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="3">
+        <v>20000.0</v>
+      </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="F38" s="1">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G38" s="1">
-        <v>40.0</v>
+        <v>9.0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I38" s="1">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="J38" s="1">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="K38" s="1">
         <v>3.0</v>
@@ -2614,40 +2653,42 @@
         <v>10.0</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q38" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R38" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S38" s="1">
         <v>6.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="E39" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F39" s="1">
         <v>8.0</v>
       </c>
       <c r="G39" s="1">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I39" s="1">
-        <v>22.5</v>
+        <v>5.0</v>
       </c>
       <c r="J39" s="1">
-        <v>22.5</v>
+        <v>5.0</v>
       </c>
       <c r="K39" s="1">
         <v>3.0</v>
@@ -2665,7 +2706,7 @@
         <v>10.0</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="P39:P48" si="3">4*12</f>
         <v>48</v>
       </c>
       <c r="Q39" s="1">
@@ -2683,34 +2724,34 @@
     </row>
     <row r="40">
       <c r="E40" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F40" s="1">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G40" s="1">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I40" s="1">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="J40" s="1">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="K40" s="1">
         <v>3.0</v>
       </c>
       <c r="L40" s="1">
-        <v>1.0</v>
+        <v>32.0</v>
       </c>
       <c r="M40" s="1">
         <v>3.0</v>
       </c>
       <c r="N40" s="1">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="O40" s="1">
         <v>10.0</v>
@@ -2733,26 +2774,23 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F41" s="1">
         <v>8.0</v>
       </c>
       <c r="G41" s="1">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I41" s="1">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="J41" s="1">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="K41" s="1">
         <v>3.0</v>
@@ -2770,16 +2808,17 @@
         <v>10.0</v>
       </c>
       <c r="P41" s="1">
-        <v>24.0</v>
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="Q41" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R41" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S41" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
         <v>22</v>
@@ -2787,13 +2826,13 @@
     </row>
     <row r="42">
       <c r="E42" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F42" s="1">
         <v>8.0</v>
       </c>
       <c r="G42" s="1">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>22</v>
@@ -2802,34 +2841,35 @@
         <v>10.0</v>
       </c>
       <c r="J42" s="1">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="K42" s="1">
         <v>3.0</v>
       </c>
       <c r="L42" s="1">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="M42" s="1">
         <v>3.0</v>
       </c>
       <c r="N42" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="O42" s="1">
         <v>10.0</v>
       </c>
       <c r="P42" s="1">
-        <v>24.0</v>
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="Q42" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R42" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S42" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
         <v>22</v>
@@ -2837,22 +2877,22 @@
     </row>
     <row r="43">
       <c r="E43" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F43" s="1">
         <v>8.0</v>
       </c>
       <c r="G43" s="1">
-        <v>15.0</v>
+        <v>25.0</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I43" s="1">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="J43" s="1">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="K43" s="1">
         <v>3.0</v>
@@ -2870,16 +2910,17 @@
         <v>10.0</v>
       </c>
       <c r="P43" s="1">
-        <v>24.0</v>
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="Q43" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R43" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S43" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
         <v>22</v>
@@ -2887,22 +2928,22 @@
     </row>
     <row r="44">
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F44" s="1">
         <v>8.0</v>
       </c>
       <c r="G44" s="1">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I44" s="1">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="J44" s="1">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="K44" s="1">
         <v>3.0</v>
@@ -2920,16 +2961,17 @@
         <v>10.0</v>
       </c>
       <c r="P44" s="1">
-        <v>24.0</v>
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="Q44" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R44" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S44" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
         <v>22</v>
@@ -2937,22 +2979,22 @@
     </row>
     <row r="45">
       <c r="E45" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F45" s="1">
         <v>8.0</v>
       </c>
       <c r="G45" s="1">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I45" s="1">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="J45" s="1">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="K45" s="1">
         <v>3.0</v>
@@ -2970,16 +3012,17 @@
         <v>10.0</v>
       </c>
       <c r="P45" s="1">
-        <v>24.0</v>
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="Q45" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R45" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S45" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
         <v>22</v>
@@ -2987,22 +3030,22 @@
     </row>
     <row r="46">
       <c r="E46" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F46" s="1">
         <v>8.0</v>
       </c>
       <c r="G46" s="1">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I46" s="1">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="J46" s="1">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="K46" s="1">
         <v>3.0</v>
@@ -3020,16 +3063,17 @@
         <v>10.0</v>
       </c>
       <c r="P46" s="1">
-        <v>24.0</v>
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="Q46" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R46" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S46" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
         <v>22</v>
@@ -3037,22 +3081,22 @@
     </row>
     <row r="47">
       <c r="E47" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F47" s="1">
         <v>8.0</v>
       </c>
       <c r="G47" s="1">
-        <v>35.0</v>
+        <v>45.0</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I47" s="1">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="J47" s="1">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="K47" s="1">
         <v>3.0</v>
@@ -3070,16 +3114,17 @@
         <v>10.0</v>
       </c>
       <c r="P47" s="1">
-        <v>24.0</v>
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="Q47" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R47" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S47" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
         <v>22</v>
@@ -3087,28 +3132,28 @@
     </row>
     <row r="48">
       <c r="E48" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F48" s="1">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G48" s="1">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I48" s="1">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="J48" s="1">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="K48" s="1">
         <v>3.0</v>
       </c>
       <c r="L48" s="1">
-        <v>31.0</v>
+        <v>1.0</v>
       </c>
       <c r="M48" s="1">
         <v>3.0</v>
@@ -3120,39 +3165,43 @@
         <v>10.0</v>
       </c>
       <c r="P48" s="1">
-        <v>24.0</v>
+        <f t="shared" si="3"/>
+        <v>48</v>
       </c>
       <c r="Q48" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R48" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S48" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="E49" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
       </c>
       <c r="G49" s="1">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I49" s="1">
-        <v>22.5</v>
+        <v>5.0</v>
       </c>
       <c r="J49" s="1">
-        <v>22.5</v>
+        <v>5.0</v>
       </c>
       <c r="K49" s="1">
         <v>3.0</v>
@@ -3187,34 +3236,34 @@
     </row>
     <row r="50">
       <c r="E50" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F50" s="1">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="G50" s="1">
-        <v>50.0</v>
+        <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I50" s="1">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="J50" s="1">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="K50" s="1">
         <v>3.0</v>
       </c>
       <c r="L50" s="1">
-        <v>1.0</v>
+        <v>32.0</v>
       </c>
       <c r="M50" s="1">
         <v>3.0</v>
       </c>
       <c r="N50" s="1">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="O50" s="1">
         <v>10.0</v>
@@ -3236,26 +3285,23 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F51" s="1">
         <v>8.0</v>
       </c>
       <c r="G51" s="1">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I51" s="1">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="J51" s="1">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="K51" s="1">
         <v>3.0</v>
@@ -3272,19 +3318,31 @@
       <c r="O51" s="1">
         <v>10.0</v>
       </c>
+      <c r="P51" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S51" s="1">
+        <v>3.0</v>
+      </c>
       <c r="T51" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="E52" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1">
         <v>8.0</v>
       </c>
       <c r="G52" s="1">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>22</v>
@@ -3293,22 +3351,34 @@
         <v>10.0</v>
       </c>
       <c r="J52" s="1">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="K52" s="1">
         <v>3.0</v>
       </c>
       <c r="L52" s="1">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="M52" s="1">
         <v>3.0</v>
       </c>
       <c r="N52" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="O52" s="1">
         <v>10.0</v>
+      </c>
+      <c r="P52" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S52" s="1">
+        <v>3.0</v>
       </c>
       <c r="T52" s="1" t="s">
         <v>22</v>
@@ -3316,22 +3386,22 @@
     </row>
     <row r="53">
       <c r="E53" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F53" s="1">
         <v>8.0</v>
       </c>
       <c r="G53" s="1">
-        <v>15.0</v>
+        <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I53" s="1">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="J53" s="1">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="K53" s="1">
         <v>3.0</v>
@@ -3348,28 +3418,40 @@
       <c r="O53" s="1">
         <v>10.0</v>
       </c>
+      <c r="P53" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S53" s="1">
+        <v>3.0</v>
+      </c>
       <c r="T53" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54">
       <c r="E54" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F54" s="1">
         <v>8.0</v>
       </c>
       <c r="G54" s="1">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I54" s="1">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="J54" s="1">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="K54" s="1">
         <v>3.0</v>
@@ -3386,28 +3468,40 @@
       <c r="O54" s="1">
         <v>10.0</v>
       </c>
+      <c r="P54" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S54" s="1">
+        <v>3.0</v>
+      </c>
       <c r="T54" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="E55" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F55" s="1">
         <v>8.0</v>
       </c>
       <c r="G55" s="1">
-        <v>25.0</v>
+        <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I55" s="1">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="J55" s="1">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="K55" s="1">
         <v>3.0</v>
@@ -3424,28 +3518,40 @@
       <c r="O55" s="1">
         <v>10.0</v>
       </c>
+      <c r="P55" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>3.0</v>
+      </c>
       <c r="T55" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="56">
       <c r="E56" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F56" s="1">
         <v>8.0</v>
       </c>
       <c r="G56" s="1">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I56" s="1">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="J56" s="1">
-        <v>15.0</v>
+        <v>20.0</v>
       </c>
       <c r="K56" s="1">
         <v>3.0</v>
@@ -3462,28 +3568,40 @@
       <c r="O56" s="1">
         <v>10.0</v>
       </c>
+      <c r="P56" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>3.0</v>
+      </c>
       <c r="T56" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F57" s="1">
         <v>8.0</v>
       </c>
       <c r="G57" s="1">
-        <v>35.0</v>
+        <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I57" s="1">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="J57" s="1">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="K57" s="1">
         <v>3.0</v>
@@ -3500,34 +3618,46 @@
       <c r="O57" s="1">
         <v>10.0</v>
       </c>
+      <c r="P57" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S57" s="1">
+        <v>3.0</v>
+      </c>
       <c r="T57" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="E58" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F58" s="1">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G58" s="1">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I58" s="1">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="J58" s="1">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="K58" s="1">
         <v>3.0</v>
       </c>
       <c r="L58" s="1">
-        <v>31.0</v>
+        <v>1.0</v>
       </c>
       <c r="M58" s="1">
         <v>3.0</v>
@@ -3538,28 +3668,43 @@
       <c r="O58" s="1">
         <v>10.0</v>
       </c>
+      <c r="P58" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S58" s="1">
+        <v>3.0</v>
+      </c>
       <c r="T58" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E59" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
       </c>
       <c r="G59" s="1">
-        <v>45.0</v>
+        <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I59" s="1">
-        <v>22.5</v>
+        <v>5.0</v>
       </c>
       <c r="J59" s="1">
-        <v>22.5</v>
+        <v>5.0</v>
       </c>
       <c r="K59" s="1">
         <v>3.0</v>
@@ -3576,45 +3721,469 @@
       <c r="O59" s="1">
         <v>10.0</v>
       </c>
+      <c r="P59" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R59" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S59" s="2">
+        <v>18.0</v>
+      </c>
       <c r="T59" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J60" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K60" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L60" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="M60" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N60" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="O60" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P60" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R60" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="E61" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="J61" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K61" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L61" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M61" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N61" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O61" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P61" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R61" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S61" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T61" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="E62" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F62" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I62" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J62" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K62" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L62" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M62" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N62" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O62" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P62" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R62" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S62" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T62" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="E63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I63" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="J63" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="K63" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L63" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O63" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P63" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R63" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T63" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="E64" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I64" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="J64" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="K64" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L64" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M64" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N64" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O64" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P64" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R64" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S64" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="E65" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="J65" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="K65" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L65" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M65" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N65" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O65" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P65" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R65" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S65" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="E66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F66" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J66" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K66" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L66" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M66" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O66" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P66" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R66" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S66" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="E67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="J67" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="K67" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L67" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M67" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O67" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P67" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R67" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S67" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T67" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F60" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G60" s="1">
+      <c r="F68" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G68" s="1">
         <v>50.0</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I60" s="1">
+      <c r="H68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="1">
         <v>25.0</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J68" s="1">
         <v>25.0</v>
       </c>
-      <c r="K60" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L60" s="1">
+      <c r="K68" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L68" s="1">
         <v>1.0</v>
       </c>
-      <c r="M60" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N60" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O60" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="T60" s="1" t="s">
+      <c r="M68" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P68" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R68" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S68" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T68" s="1" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3640,26 +4209,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -4681,58 +5250,58 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -4740,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
@@ -4748,7 +5317,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -4756,7 +5325,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
@@ -4764,7 +5333,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -4772,7 +5341,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -4780,7 +5349,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -4788,7 +5357,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -4796,7 +5365,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -4804,7 +5373,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
@@ -4812,23 +5381,23 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
@@ -4836,7 +5405,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
@@ -4844,23 +5413,23 @@
         <v>15</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,45 +15,93 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="96">
   <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
     <t>Project</t>
   </si>
   <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>BUA</t>
   </si>
   <si>
     <t>Phase</t>
   </si>
   <si>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
     <t>Plan</t>
   </si>
   <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
     <t>Years</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
     <t>Discount %</t>
   </si>
   <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
     <t>Down Payment Type</t>
   </si>
   <si>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+  </si>
+  <si>
     <t>DP2 Due (months)</t>
   </si>
   <si>
     <t>Installments Count</t>
   </si>
   <si>
+    <t>Column</t>
+  </si>
+  <si>
     <t>Installment Every (months)</t>
   </si>
   <si>
+    <t>Meaning / المعنى</t>
+  </si>
+  <si>
     <t>First Installment Due (months)</t>
   </si>
   <si>
@@ -72,18 +120,72 @@
     <t>Maintenance Basis</t>
   </si>
   <si>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+  </si>
+  <si>
     <t>YOUD</t>
   </si>
   <si>
     <t>YOUD &amp; YOUD EL BAHR</t>
   </si>
   <si>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+  </si>
+  <si>
+    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
+  </si>
+  <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+  </si>
+  <si>
     <t>Original Price</t>
   </si>
   <si>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
+  </si>
+  <si>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
+  </si>
+  <si>
+    <t>Number of equal installments / عدد الأقساط</t>
+  </si>
+  <si>
+    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
+  </si>
+  <si>
+    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
+  </si>
+  <si>
+    <t>Admin Fee %</t>
+  </si>
+  <si>
+    <t>% of system price, paid upfront / رسوم إدارية</t>
+  </si>
+  <si>
+    <t>Operations Fee %</t>
+  </si>
+  <si>
+    <t>% of system price, paid upfront / رسوم تشغيل</t>
+  </si>
+  <si>
+    <t>% of system price, due at delivery / وديعة الصيانة</t>
+  </si>
+  <si>
+    <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
+  </si>
+  <si>
+    <t>After editing: save the file, then refresh the page in the browser.</t>
+  </si>
+  <si>
+    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
+  </si>
+  <si>
     <t>Selling price</t>
   </si>
   <si>
@@ -199,108 +301,6 @@
   </si>
   <si>
     <t>GAIA</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>Alahly Sabbour</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>How to fill the Projects sheet</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
-  </si>
-  <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
-  </si>
-  <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Meaning / المعنى</t>
-  </si>
-  <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
-  </si>
-  <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
-  </si>
-  <si>
-    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
-  </si>
-  <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
-  </si>
-  <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
-  </si>
-  <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
-  </si>
-  <si>
-    <t>Number of equal installments / عدد الأقساط</t>
-  </si>
-  <si>
-    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
-  </si>
-  <si>
-    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
-  </si>
-  <si>
-    <t>Admin Fee %</t>
-  </si>
-  <si>
-    <t>% of system price, paid upfront / رسوم إدارية</t>
-  </si>
-  <si>
-    <t>Operations Fee %</t>
-  </si>
-  <si>
-    <t>% of system price, paid upfront / رسوم تشغيل</t>
-  </si>
-  <si>
-    <t>% of system price, due at delivery / وديعة الصيانة</t>
-  </si>
-  <si>
-    <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
-  </si>
-  <si>
-    <t>After editing: save the file, then refresh the page in the browser.</t>
-  </si>
-  <si>
-    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
   </si>
 </sst>
 </file>
@@ -350,10 +350,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -600,75 +600,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -715,15 +715,15 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="s">
-        <v>20</v>
+      <c r="B3" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F3" s="1">
         <v>8.0</v>
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -770,15 +770,15 @@
         <v>6.0</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="s">
-        <v>20</v>
+      <c r="B4" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F4" s="1">
         <v>8.0</v>
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -825,15 +825,15 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="s">
-        <v>20</v>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F5" s="1">
         <v>8.0</v>
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -879,15 +879,15 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="s">
-        <v>20</v>
+      <c r="B6" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F6" s="1">
         <v>8.0</v>
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -933,15 +933,15 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="s">
-        <v>20</v>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F7" s="1">
         <v>8.0</v>
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -987,15 +987,15 @@
         <v>6.0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="s">
-        <v>20</v>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F8" s="1">
         <v>8.0</v>
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1041,15 +1041,15 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="s">
-        <v>20</v>
+      <c r="B9" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F9" s="1">
         <v>8.0</v>
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1095,15 +1095,15 @@
         <v>6.0</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="s">
-        <v>20</v>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="F10" s="1">
         <v>8.0</v>
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1149,18 +1149,18 @@
         <v>6.0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="s">
-        <v>20</v>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="F11" s="1">
         <v>0.0</v>
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1195,28 +1195,28 @@
       <c r="P11" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q11" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R11" s="2">
+      <c r="Q11" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R11" s="3">
         <v>18.0</v>
       </c>
       <c r="S11" s="1">
         <v>6.0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="3">
         <v>4.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="F12" s="1">
         <v>0.0</v>
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1262,15 +1262,15 @@
         <v>6.0</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="F13" s="1">
         <v>2.0</v>
@@ -1279,7 +1279,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I13" s="1">
         <v>10.0</v>
@@ -1315,15 +1315,15 @@
         <v>3.0</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="F14" s="1">
         <v>3.0</v>
@@ -1332,20 +1332,19 @@
         <v>0.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="J14" s="1">
-        <v>7.5</v>
+        <v>43</v>
+      </c>
+      <c r="I14" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.0</v>
       </c>
       <c r="K14" s="1">
         <v>3.0</v>
       </c>
-      <c r="L14" s="1">
-        <f>3*4-1</f>
-        <v>11</v>
+      <c r="L14" s="3">
+        <v>12.0</v>
       </c>
       <c r="M14" s="1">
         <v>3.0</v>
@@ -1369,15 +1368,15 @@
         <v>3.0</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="F15" s="1">
         <v>4.0</v>
@@ -1386,20 +1385,19 @@
         <v>0.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>10.0</v>
+        <v>43</v>
+      </c>
+      <c r="I15" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0.0</v>
       </c>
       <c r="K15" s="1">
         <v>3.0</v>
       </c>
-      <c r="L15" s="1">
-        <f>4*4-1</f>
-        <v>15</v>
+      <c r="L15" s="3">
+        <v>16.0</v>
       </c>
       <c r="M15" s="1">
         <v>3.0</v>
@@ -1423,15 +1421,15 @@
         <v>3.0</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="F16" s="1">
         <v>5.0</v>
@@ -1440,20 +1438,19 @@
         <v>0.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="1">
-        <v>12.5</v>
-      </c>
-      <c r="J16" s="1">
-        <v>12.5</v>
+        <v>43</v>
+      </c>
+      <c r="I16" s="3">
+        <v>25.0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>0.0</v>
       </c>
       <c r="K16" s="1">
         <v>3.0</v>
       </c>
-      <c r="L16" s="1">
-        <f>5*4-1</f>
-        <v>19</v>
+      <c r="L16" s="3">
+        <v>20.0</v>
       </c>
       <c r="M16" s="1">
         <v>3.0</v>
@@ -1477,15 +1474,15 @@
         <v>3.0</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F17" s="1">
         <v>6.0</v>
@@ -1494,20 +1491,19 @@
         <v>0.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>15.0</v>
+        <v>43</v>
+      </c>
+      <c r="I17" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0.0</v>
       </c>
       <c r="K17" s="1">
         <v>3.0</v>
       </c>
-      <c r="L17" s="1">
-        <f>6*4-1</f>
-        <v>23</v>
+      <c r="L17" s="3">
+        <v>24.0</v>
       </c>
       <c r="M17" s="1">
         <v>3.0</v>
@@ -1531,15 +1527,15 @@
         <v>3.0</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="F18" s="1">
         <v>7.0</v>
@@ -1548,20 +1544,19 @@
         <v>0.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="1">
-        <v>17.5</v>
-      </c>
-      <c r="J18" s="1">
-        <v>17.5</v>
+        <v>43</v>
+      </c>
+      <c r="I18" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0.0</v>
       </c>
       <c r="K18" s="1">
         <v>3.0</v>
       </c>
-      <c r="L18" s="1">
-        <f>7*4-1</f>
-        <v>27</v>
+      <c r="L18" s="3">
+        <v>28.0</v>
       </c>
       <c r="M18" s="1">
         <v>3.0</v>
@@ -1585,15 +1580,15 @@
         <v>3.0</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="F19" s="1">
         <v>8.0</v>
@@ -1602,20 +1597,19 @@
         <v>0.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="1">
-        <v>20.0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>20.0</v>
+        <v>43</v>
+      </c>
+      <c r="I19" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0.0</v>
       </c>
       <c r="K19" s="1">
         <v>3.0</v>
       </c>
-      <c r="L19" s="1">
-        <f>8*4-1</f>
-        <v>31</v>
+      <c r="L19" s="3">
+        <v>32.0</v>
       </c>
       <c r="M19" s="1">
         <v>3.0</v>
@@ -1639,15 +1633,15 @@
         <v>3.0</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="F20" s="1">
         <v>0.0</v>
@@ -1656,7 +1650,7 @@
         <v>15.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I20" s="1">
         <v>100.0</v>
@@ -1692,443 +1686,443 @@
         <v>3.0</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="2">
+      <c r="B21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="3">
         <v>4.0</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>0.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="J21" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="2">
+        <v>43</v>
+      </c>
+      <c r="I21" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="3">
         <v>0.0</v>
       </c>
       <c r="L21" s="1">
         <f>4*4</f>
         <v>16</v>
       </c>
-      <c r="M21" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N21" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O21" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P21" s="2">
+      <c r="M21" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O21" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P21" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q21" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R21" s="2">
+      <c r="Q21" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R21" s="3">
         <v>15.0</v>
       </c>
-      <c r="S21" s="2">
+      <c r="S21" s="3">
         <v>3.0</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F22" s="2">
+      <c r="B22" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="3">
         <v>5.0</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="3">
         <v>0.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="2">
+        <v>43</v>
+      </c>
+      <c r="I22" s="3">
         <v>7.5</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="3">
         <v>7.5</v>
       </c>
-      <c r="K22" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L22" s="2">
+      <c r="K22" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L22" s="3">
         <v>19.0</v>
       </c>
-      <c r="M22" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N22" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O22" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P22" s="2">
+      <c r="M22" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N22" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O22" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P22" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q22" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R22" s="2">
+      <c r="Q22" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R22" s="3">
         <v>15.0</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S22" s="3">
         <v>3.0</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F23" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="G23" s="2">
+      <c r="B23" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="G23" s="3">
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="J23" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="K23" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L23" s="2">
+        <v>43</v>
+      </c>
+      <c r="I23" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L23" s="3">
         <v>23.0</v>
       </c>
-      <c r="M23" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N23" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O23" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P23" s="2">
+      <c r="M23" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N23" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O23" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P23" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q23" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R23" s="2">
+      <c r="Q23" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R23" s="3">
         <v>15.0</v>
       </c>
-      <c r="S23" s="2">
+      <c r="S23" s="3">
         <v>3.0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F24" s="2">
+      <c r="B24" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="3">
         <v>7.0</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="3">
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="2">
+        <v>43</v>
+      </c>
+      <c r="I24" s="3">
         <v>12.5</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="3">
         <v>12.5</v>
       </c>
-      <c r="K24" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L24" s="2">
+      <c r="K24" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L24" s="3">
         <v>27.0</v>
       </c>
-      <c r="M24" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N24" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O24" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P24" s="2">
+      <c r="M24" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P24" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q24" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R24" s="2">
+      <c r="Q24" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R24" s="3">
         <v>15.0</v>
       </c>
-      <c r="S24" s="2">
+      <c r="S24" s="3">
         <v>3.0</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="2">
+      <c r="B25" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="3">
         <v>8.0</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="3">
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="2">
+        <v>43</v>
+      </c>
+      <c r="I25" s="3">
         <v>15.0</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="3">
         <v>15.0</v>
       </c>
-      <c r="K25" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L25" s="2">
+      <c r="K25" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L25" s="3">
         <v>31.0</v>
       </c>
-      <c r="M25" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N25" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O25" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P25" s="2">
+      <c r="M25" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N25" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P25" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q25" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R25" s="2">
+      <c r="Q25" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R25" s="3">
         <v>15.0</v>
       </c>
-      <c r="S25" s="2">
+      <c r="S25" s="3">
         <v>3.0</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F26" s="2">
+      <c r="B26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="3">
         <v>9.0</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="3">
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="2">
+        <v>43</v>
+      </c>
+      <c r="I26" s="3">
         <v>17.5</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="3">
         <v>17.5</v>
       </c>
-      <c r="K26" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L26" s="2">
+      <c r="K26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L26" s="3">
         <v>35.0</v>
       </c>
-      <c r="M26" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N26" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O26" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P26" s="2">
+      <c r="M26" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N26" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O26" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P26" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q26" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R26" s="2">
+      <c r="Q26" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R26" s="3">
         <v>15.0</v>
       </c>
-      <c r="S26" s="2">
+      <c r="S26" s="3">
         <v>3.0</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F27" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="G27" s="2">
+      <c r="B27" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G27" s="3">
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="2">
+        <v>43</v>
+      </c>
+      <c r="I27" s="3">
         <v>20.0</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="3">
         <v>20.0</v>
       </c>
-      <c r="K27" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L27" s="2">
+      <c r="K27" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L27" s="3">
         <v>39.0</v>
       </c>
-      <c r="M27" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N27" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O27" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P27" s="2">
+      <c r="M27" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N27" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O27" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P27" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q27" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R27" s="2">
+      <c r="Q27" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R27" s="3">
         <v>15.0</v>
       </c>
-      <c r="S27" s="2">
+      <c r="S27" s="3">
         <v>3.0</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="2" t="s">
-        <v>43</v>
+      <c r="B28" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="2">
+        <v>76</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G28" s="3">
         <v>15.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="2">
+        <v>57</v>
+      </c>
+      <c r="I28" s="3">
         <v>100.0</v>
       </c>
-      <c r="J28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="O28" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P28" s="2">
+      <c r="J28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="M28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P28" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q28" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R28" s="2">
+      <c r="Q28" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R28" s="3">
         <v>15.0</v>
       </c>
-      <c r="S28" s="2">
+      <c r="S28" s="3">
         <v>3.0</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F29" s="1">
         <v>0.0</v>
@@ -2137,7 +2131,7 @@
         <v>25.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I29" s="1">
         <v>100.0</v>
@@ -2173,15 +2167,15 @@
         <v>6.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F30" s="1">
         <v>8.0</v>
@@ -2190,7 +2184,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I30" s="1">
         <v>5.0</v>
@@ -2226,15 +2220,15 @@
         <v>6.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="F31" s="1">
         <v>7.0</v>
@@ -2243,7 +2237,7 @@
         <v>3.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I31" s="1">
         <v>5.0</v>
@@ -2279,15 +2273,15 @@
         <v>6.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="F32" s="1">
         <v>6.0</v>
@@ -2296,7 +2290,7 @@
         <v>6.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I32" s="1">
         <v>5.0</v>
@@ -2332,15 +2326,15 @@
         <v>6.0</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="F33" s="1">
         <v>5.0</v>
@@ -2349,7 +2343,7 @@
         <v>9.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I33" s="1">
         <v>5.0</v>
@@ -2385,18 +2379,18 @@
         <v>6.0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="3">
+        <v>92</v>
+      </c>
+      <c r="C34" s="4">
         <v>20000.0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="F34" s="1">
         <v>0.0</v>
@@ -2405,7 +2399,7 @@
         <v>25.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I34" s="1">
         <v>100.0</v>
@@ -2441,18 +2435,18 @@
         <v>6.0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="3">
+        <v>92</v>
+      </c>
+      <c r="C35" s="4">
         <v>20000.0</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F35" s="1">
         <v>8.0</v>
@@ -2461,7 +2455,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I35" s="1">
         <v>5.0</v>
@@ -2497,18 +2491,18 @@
         <v>6.0</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C36" s="3">
+        <v>92</v>
+      </c>
+      <c r="C36" s="4">
         <v>20000.0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="F36" s="1">
         <v>7.0</v>
@@ -2517,7 +2511,7 @@
         <v>3.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I36" s="1">
         <v>5.0</v>
@@ -2553,18 +2547,18 @@
         <v>6.0</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="3">
+        <v>92</v>
+      </c>
+      <c r="C37" s="4">
         <v>20000.0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="F37" s="1">
         <v>6.0</v>
@@ -2573,7 +2567,7 @@
         <v>6.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I37" s="1">
         <v>5.0</v>
@@ -2609,18 +2603,18 @@
         <v>6.0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="3">
+        <v>92</v>
+      </c>
+      <c r="C38" s="4">
         <v>20000.0</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="F38" s="1">
         <v>5.0</v>
@@ -2629,7 +2623,7 @@
         <v>9.0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I38" s="1">
         <v>5.0</v>
@@ -2665,15 +2659,15 @@
         <v>6.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F39" s="1">
         <v>8.0</v>
@@ -2682,7 +2676,7 @@
         <v>0.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I39" s="1">
         <v>5.0</v>
@@ -2719,12 +2713,12 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
       <c r="E40" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F40" s="1">
         <v>8.0</v>
@@ -2733,7 +2727,7 @@
         <v>10.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I40" s="1">
         <v>10.0</v>
@@ -2770,12 +2764,12 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
       <c r="E41" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F41" s="1">
         <v>8.0</v>
@@ -2784,7 +2778,7 @@
         <v>15.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I41" s="1">
         <v>7.5</v>
@@ -2821,12 +2815,12 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42">
       <c r="E42" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F42" s="1">
         <v>8.0</v>
@@ -2835,7 +2829,7 @@
         <v>20.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I42" s="1">
         <v>10.0</v>
@@ -2872,12 +2866,12 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
       <c r="E43" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F43" s="1">
         <v>8.0</v>
@@ -2886,7 +2880,7 @@
         <v>25.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I43" s="1">
         <v>12.5</v>
@@ -2923,12 +2917,12 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
       <c r="E44" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F44" s="1">
         <v>8.0</v>
@@ -2937,7 +2931,7 @@
         <v>30.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I44" s="1">
         <v>15.0</v>
@@ -2974,12 +2968,12 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
       <c r="E45" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F45" s="1">
         <v>8.0</v>
@@ -2988,7 +2982,7 @@
         <v>35.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I45" s="1">
         <v>17.5</v>
@@ -3025,12 +3019,12 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
       <c r="E46" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F46" s="1">
         <v>8.0</v>
@@ -3039,7 +3033,7 @@
         <v>40.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I46" s="1">
         <v>20.0</v>
@@ -3076,12 +3070,12 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
       <c r="E47" s="1" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="F47" s="1">
         <v>8.0</v>
@@ -3090,7 +3084,7 @@
         <v>45.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I47" s="1">
         <v>22.5</v>
@@ -3127,12 +3121,12 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48">
       <c r="E48" s="1" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="F48" s="1">
         <v>0.0</v>
@@ -3141,7 +3135,7 @@
         <v>50.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I48" s="1">
         <v>25.0</v>
@@ -3178,15 +3172,15 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3195,7 +3189,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3231,12 +3225,12 @@
         <v>3.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F50" s="1">
         <v>8.0</v>
@@ -3245,7 +3239,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3281,12 +3275,12 @@
         <v>3.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
       <c r="E51" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F51" s="1">
         <v>8.0</v>
@@ -3295,7 +3289,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3331,12 +3325,12 @@
         <v>3.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
       <c r="E52" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F52" s="1">
         <v>8.0</v>
@@ -3345,7 +3339,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3381,12 +3375,12 @@
         <v>3.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
       <c r="E53" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F53" s="1">
         <v>8.0</v>
@@ -3395,7 +3389,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3431,12 +3425,12 @@
         <v>3.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54">
       <c r="E54" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F54" s="1">
         <v>8.0</v>
@@ -3445,7 +3439,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3481,12 +3475,12 @@
         <v>3.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
       <c r="E55" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F55" s="1">
         <v>8.0</v>
@@ -3495,7 +3489,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3531,12 +3525,12 @@
         <v>3.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
       <c r="E56" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F56" s="1">
         <v>8.0</v>
@@ -3545,7 +3539,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3581,12 +3575,12 @@
         <v>3.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="1" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="F57" s="1">
         <v>8.0</v>
@@ -3595,7 +3589,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3631,12 +3625,12 @@
         <v>3.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58">
       <c r="E58" s="1" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="F58" s="1">
         <v>0.0</v>
@@ -3645,7 +3639,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3681,15 +3675,15 @@
         <v>3.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="s">
-        <v>61</v>
+      <c r="A59" s="3" t="s">
+        <v>95</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3698,7 +3692,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3721,25 +3715,25 @@
       <c r="O59" s="1">
         <v>10.0</v>
       </c>
-      <c r="P59" s="2">
+      <c r="P59" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q59" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R59" s="2">
+      <c r="Q59" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R59" s="3">
         <v>30.0</v>
       </c>
-      <c r="S59" s="2">
+      <c r="S59" s="3">
         <v>18.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F60" s="1">
         <v>8.0</v>
@@ -3748,7 +3742,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3771,25 +3765,25 @@
       <c r="O60" s="1">
         <v>10.0</v>
       </c>
-      <c r="P60" s="2">
+      <c r="P60" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q60" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R60" s="2">
+      <c r="Q60" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R60" s="3">
         <v>30.0</v>
       </c>
-      <c r="S60" s="2">
+      <c r="S60" s="3">
         <v>18.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61">
       <c r="E61" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1">
         <v>8.0</v>
@@ -3798,7 +3792,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3821,25 +3815,25 @@
       <c r="O61" s="1">
         <v>10.0</v>
       </c>
-      <c r="P61" s="2">
+      <c r="P61" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q61" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R61" s="2">
+      <c r="Q61" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R61" s="3">
         <v>30.0</v>
       </c>
-      <c r="S61" s="2">
+      <c r="S61" s="3">
         <v>18.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62">
       <c r="E62" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F62" s="1">
         <v>8.0</v>
@@ -3848,7 +3842,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3871,25 +3865,25 @@
       <c r="O62" s="1">
         <v>10.0</v>
       </c>
-      <c r="P62" s="2">
+      <c r="P62" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q62" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R62" s="2">
+      <c r="Q62" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R62" s="3">
         <v>30.0</v>
       </c>
-      <c r="S62" s="2">
+      <c r="S62" s="3">
         <v>18.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
       <c r="E63" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F63" s="1">
         <v>8.0</v>
@@ -3898,7 +3892,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3921,25 +3915,25 @@
       <c r="O63" s="1">
         <v>10.0</v>
       </c>
-      <c r="P63" s="2">
+      <c r="P63" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q63" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R63" s="2">
+      <c r="Q63" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R63" s="3">
         <v>30.0</v>
       </c>
-      <c r="S63" s="2">
+      <c r="S63" s="3">
         <v>18.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
       <c r="E64" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F64" s="1">
         <v>8.0</v>
@@ -3948,7 +3942,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -3971,25 +3965,25 @@
       <c r="O64" s="1">
         <v>10.0</v>
       </c>
-      <c r="P64" s="2">
+      <c r="P64" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q64" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R64" s="2">
+      <c r="Q64" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R64" s="3">
         <v>30.0</v>
       </c>
-      <c r="S64" s="2">
+      <c r="S64" s="3">
         <v>18.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F65" s="1">
         <v>8.0</v>
@@ -3998,7 +3992,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4021,25 +4015,25 @@
       <c r="O65" s="1">
         <v>10.0</v>
       </c>
-      <c r="P65" s="2">
+      <c r="P65" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q65" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R65" s="2">
+      <c r="Q65" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R65" s="3">
         <v>30.0</v>
       </c>
-      <c r="S65" s="2">
+      <c r="S65" s="3">
         <v>18.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
       <c r="E66" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F66" s="1">
         <v>8.0</v>
@@ -4048,7 +4042,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4071,25 +4065,25 @@
       <c r="O66" s="1">
         <v>10.0</v>
       </c>
-      <c r="P66" s="2">
+      <c r="P66" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q66" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R66" s="2">
+      <c r="Q66" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R66" s="3">
         <v>30.0</v>
       </c>
-      <c r="S66" s="2">
+      <c r="S66" s="3">
         <v>18.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67">
       <c r="E67" s="1" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="F67" s="1">
         <v>8.0</v>
@@ -4098,7 +4092,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4121,25 +4115,25 @@
       <c r="O67" s="1">
         <v>10.0</v>
       </c>
-      <c r="P67" s="2">
+      <c r="P67" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q67" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R67" s="2">
+      <c r="Q67" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R67" s="3">
         <v>30.0</v>
       </c>
-      <c r="S67" s="2">
+      <c r="S67" s="3">
         <v>18.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68">
       <c r="E68" s="1" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="F68" s="1">
         <v>0.0</v>
@@ -4148,7 +4142,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4171,20 +4165,20 @@
       <c r="O68" s="1">
         <v>10.0</v>
       </c>
-      <c r="P68" s="2">
+      <c r="P68" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q68" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R68" s="2">
+      <c r="Q68" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R68" s="3">
         <v>30.0</v>
       </c>
-      <c r="S68" s="2">
+      <c r="S68" s="3">
         <v>18.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4209,26 +4203,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5250,186 +5244,186 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>73</v>
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>75</v>
+        <v>21</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>77</v>
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>78</v>
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>81</v>
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>84</v>
+        <v>24</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>86</v>
+        <v>27</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>93</v>
+        <v>31</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>95</v>
+        <v>55</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,91 +15,97 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="96">
   <si>
+    <t>Setting</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
     <t>Project</t>
   </si>
   <si>
-    <t>Setting</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>Company Name</t>
   </si>
   <si>
     <t>BUA</t>
   </si>
   <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
     <t>Phase</t>
   </si>
   <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
-    <t>Company Name</t>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
     <t>Plan</t>
   </si>
   <si>
-    <t>Alahly Sabbour</t>
-  </si>
-  <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
     <t>Years</t>
   </si>
   <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>EGP</t>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
     <t>Discount %</t>
   </si>
   <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
     <t>Down Payment Type</t>
   </si>
   <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
-  </si>
-  <si>
     <t>DP2 Due (months)</t>
   </si>
   <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Meaning / المعنى</t>
+  </si>
+  <si>
     <t>Installments Count</t>
   </si>
   <si>
-    <t>Column</t>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
     <t>Installment Every (months)</t>
   </si>
   <si>
-    <t>Meaning / المعنى</t>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
     <t>First Installment Due (months)</t>
@@ -108,63 +114,57 @@
     <t>Maintenance %</t>
   </si>
   <si>
+    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
+  </si>
+  <si>
     <t>Delivery (months)</t>
   </si>
   <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+  </si>
+  <si>
     <t>Maintenance Basis</t>
   </si>
   <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
   </si>
   <si>
     <t>YOUD</t>
   </si>
   <si>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
+  </si>
+  <si>
     <t>YOUD &amp; YOUD EL BAHR</t>
   </si>
   <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
-  </si>
-  <si>
-    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
-  </si>
-  <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+    <t>Number of equal installments / عدد الأقساط</t>
+  </si>
+  <si>
+    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
+  </si>
+  <si>
+    <t>Admin Fee %</t>
   </si>
   <si>
     <t>Original Price</t>
   </si>
   <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
-  </si>
-  <si>
-    <t>Number of equal installments / عدد الأقساط</t>
-  </si>
-  <si>
-    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
-  </si>
-  <si>
-    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
-  </si>
-  <si>
-    <t>Admin Fee %</t>
-  </si>
-  <si>
     <t>% of system price, paid upfront / رسوم إدارية</t>
   </si>
   <si>
@@ -225,19 +225,19 @@
     <t>10% DP over 2 years</t>
   </si>
   <si>
-    <t>7.5% DP &amp; 7.5% After 3 months over 3 years</t>
-  </si>
-  <si>
-    <t>10% DP &amp; 10% After 3 months over 4 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5% DP &amp; 12.5% After 3 months over 5 years </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15% DP &amp; 15% After 3 months over 6 years </t>
-  </si>
-  <si>
-    <t>17.5% DP &amp; 17.5% After 3 months over 7 years</t>
+    <t>15% DP over 3 years</t>
+  </si>
+  <si>
+    <t>20% DP over 4 years</t>
+  </si>
+  <si>
+    <t>25% DP over 5 years</t>
+  </si>
+  <si>
+    <t>30% DP over 6 years</t>
+  </si>
+  <si>
+    <t>35% DP over 7 years</t>
   </si>
   <si>
     <t>20% DP &amp; 20% After 3 months over 8 years</t>
@@ -600,75 +600,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="T1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>58</v>
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>59</v>
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>60</v>
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>61</v>
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>62</v>
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>63</v>
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>64</v>
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>65</v>
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>66</v>
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1279,7 +1279,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I13" s="1">
         <v>10.0</v>
@@ -1322,7 +1322,7 @@
       <c r="B14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F14" s="1">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I14" s="3">
         <v>15.0</v>
@@ -1375,7 +1375,7 @@
       <c r="B15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F15" s="1">
@@ -1385,7 +1385,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I15" s="3">
         <v>20.0</v>
@@ -1428,7 +1428,7 @@
       <c r="B16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F16" s="1">
@@ -1438,7 +1438,7 @@
         <v>0.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I16" s="3">
         <v>25.0</v>
@@ -1481,7 +1481,7 @@
       <c r="B17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F17" s="1">
@@ -1491,7 +1491,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I17" s="3">
         <v>30.0</v>
@@ -1534,7 +1534,7 @@
       <c r="B18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F18" s="1">
@@ -1544,7 +1544,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I18" s="3">
         <v>35.0</v>
@@ -1597,7 +1597,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I19" s="3">
         <v>40.0</v>
@@ -1703,7 +1703,7 @@
         <v>0.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I21" s="3">
         <v>10.0</v>
@@ -1757,7 +1757,7 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I22" s="3">
         <v>7.5</v>
@@ -1810,7 +1810,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I23" s="3">
         <v>10.0</v>
@@ -1863,7 +1863,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I24" s="3">
         <v>12.5</v>
@@ -1916,7 +1916,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I25" s="3">
         <v>15.0</v>
@@ -1969,7 +1969,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I26" s="3">
         <v>17.5</v>
@@ -2022,7 +2022,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I27" s="3">
         <v>20.0</v>
@@ -2167,7 +2167,7 @@
         <v>6.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
@@ -2184,7 +2184,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I30" s="1">
         <v>5.0</v>
@@ -2220,7 +2220,7 @@
         <v>6.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
@@ -2237,7 +2237,7 @@
         <v>3.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I31" s="1">
         <v>5.0</v>
@@ -2273,7 +2273,7 @@
         <v>6.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32">
@@ -2290,7 +2290,7 @@
         <v>6.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I32" s="1">
         <v>5.0</v>
@@ -2326,7 +2326,7 @@
         <v>6.0</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
@@ -2343,7 +2343,7 @@
         <v>9.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I33" s="1">
         <v>5.0</v>
@@ -2379,7 +2379,7 @@
         <v>6.0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -2667,7 +2667,7 @@
         <v>93</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F39" s="1">
         <v>8.0</v>
@@ -2676,7 +2676,7 @@
         <v>0.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I39" s="1">
         <v>5.0</v>
@@ -2713,7 +2713,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40">
@@ -2727,7 +2727,7 @@
         <v>10.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I40" s="1">
         <v>10.0</v>
@@ -2764,7 +2764,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
@@ -2778,7 +2778,7 @@
         <v>15.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I41" s="1">
         <v>7.5</v>
@@ -2815,7 +2815,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
@@ -2829,7 +2829,7 @@
         <v>20.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I42" s="1">
         <v>10.0</v>
@@ -2866,7 +2866,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43">
@@ -2880,7 +2880,7 @@
         <v>25.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I43" s="1">
         <v>12.5</v>
@@ -2917,7 +2917,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -2931,7 +2931,7 @@
         <v>30.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I44" s="1">
         <v>15.0</v>
@@ -2968,7 +2968,7 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45">
@@ -2982,7 +2982,7 @@
         <v>35.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I45" s="1">
         <v>17.5</v>
@@ -3019,7 +3019,7 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
@@ -3033,7 +3033,7 @@
         <v>40.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I46" s="1">
         <v>20.0</v>
@@ -3070,7 +3070,7 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -3084,7 +3084,7 @@
         <v>45.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I47" s="1">
         <v>22.5</v>
@@ -3121,7 +3121,7 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -3135,7 +3135,7 @@
         <v>50.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I48" s="1">
         <v>25.0</v>
@@ -3172,7 +3172,7 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -3180,7 +3180,7 @@
         <v>94</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3189,7 +3189,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3225,7 +3225,7 @@
         <v>3.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -3239,7 +3239,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3275,7 +3275,7 @@
         <v>3.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -3289,7 +3289,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3325,7 +3325,7 @@
         <v>3.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -3339,7 +3339,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3375,7 +3375,7 @@
         <v>3.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -3389,7 +3389,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3425,7 +3425,7 @@
         <v>3.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -3439,7 +3439,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3475,7 +3475,7 @@
         <v>3.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55">
@@ -3489,7 +3489,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3525,7 +3525,7 @@
         <v>3.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56">
@@ -3539,7 +3539,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3575,7 +3575,7 @@
         <v>3.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57">
@@ -3589,7 +3589,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3625,7 +3625,7 @@
         <v>3.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58">
@@ -3639,7 +3639,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3675,7 +3675,7 @@
         <v>3.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59">
@@ -3683,7 +3683,7 @@
         <v>95</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3692,7 +3692,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3728,7 +3728,7 @@
         <v>18.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60">
@@ -3742,7 +3742,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3778,7 +3778,7 @@
         <v>18.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61">
@@ -3792,7 +3792,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3828,7 +3828,7 @@
         <v>18.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62">
@@ -3842,7 +3842,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3878,7 +3878,7 @@
         <v>18.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63">
@@ -3892,7 +3892,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3928,7 +3928,7 @@
         <v>18.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64">
@@ -3942,7 +3942,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -3978,7 +3978,7 @@
         <v>18.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
@@ -3992,7 +3992,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4028,7 +4028,7 @@
         <v>18.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66">
@@ -4042,7 +4042,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4078,7 +4078,7 @@
         <v>18.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67">
@@ -4092,7 +4092,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4128,7 +4128,7 @@
         <v>18.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68">
@@ -4142,7 +4142,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4178,7 +4178,7 @@
         <v>18.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -4203,26 +4203,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5244,7 +5244,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -5260,26 +5260,26 @@
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
@@ -5292,58 +5292,58 @@
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -5351,36 +5351,36 @@
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>50</v>
@@ -5396,7 +5396,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>53</v>
@@ -5404,7 +5404,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -24,57 +24,57 @@
     <t>Project</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Value</t>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EGP</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Company Name</t>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
     <t>BUA</t>
   </si>
   <si>
-    <t>Alahly Sabbour</t>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
     <t>Phase</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
     <t>Plan</t>
   </si>
   <si>
     <t>Years</t>
   </si>
   <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
+  </si>
+  <si>
     <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
-    <t>Discount %</t>
-  </si>
-  <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
@@ -105,12 +105,12 @@
     <t>Installment Every (months)</t>
   </si>
   <si>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
-    <t>First Installment Due (months)</t>
-  </si>
-  <si>
     <t>Maintenance %</t>
   </si>
   <si>
@@ -120,61 +120,61 @@
     <t>Delivery (months)</t>
   </si>
   <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+  </si>
+  <si>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
+  </si>
+  <si>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
+  </si>
+  <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+    <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
     <t>Maintenance Basis</t>
   </si>
   <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
     <t>YOUD</t>
   </si>
   <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
+    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
   </si>
   <si>
     <t>YOUD &amp; YOUD EL BAHR</t>
   </si>
   <si>
-    <t>Number of equal installments / عدد الأقساط</t>
-  </si>
-  <si>
-    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
+    <t>Admin Fee %</t>
+  </si>
+  <si>
+    <t>% of system price, paid upfront / رسوم إدارية</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
-    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
-  </si>
-  <si>
-    <t>Admin Fee %</t>
+    <t>Operations Fee %</t>
+  </si>
+  <si>
+    <t>% of system price, paid upfront / رسوم تشغيل</t>
+  </si>
+  <si>
+    <t>% of system price, due at delivery / وديعة الصيانة</t>
   </si>
   <si>
     <t>Original Price</t>
-  </si>
-  <si>
-    <t>% of system price, paid upfront / رسوم إدارية</t>
-  </si>
-  <si>
-    <t>Operations Fee %</t>
-  </si>
-  <si>
-    <t>% of system price, paid upfront / رسوم تشغيل</t>
-  </si>
-  <si>
-    <t>% of system price, due at delivery / وديعة الصيانة</t>
   </si>
   <si>
     <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
@@ -603,13 +603,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>14</v>
@@ -618,10 +618,10 @@
         <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>21</v>
@@ -639,7 +639,7 @@
         <v>29</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>32</v>
@@ -648,27 +648,27 @@
         <v>34</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>58</v>
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>59</v>
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>60</v>
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>61</v>
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>62</v>
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>63</v>
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>64</v>
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>65</v>
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>66</v>
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1279,7 +1279,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I13" s="1">
         <v>10.0</v>
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I14" s="3">
         <v>15.0</v>
@@ -1340,8 +1340,8 @@
       <c r="J14" s="3">
         <v>0.0</v>
       </c>
-      <c r="K14" s="1">
-        <v>3.0</v>
+      <c r="K14" s="3">
+        <v>0.0</v>
       </c>
       <c r="L14" s="3">
         <v>12.0</v>
@@ -1349,8 +1349,8 @@
       <c r="M14" s="1">
         <v>3.0</v>
       </c>
-      <c r="N14" s="1">
-        <v>6.0</v>
+      <c r="N14" s="3">
+        <v>3.0</v>
       </c>
       <c r="O14" s="1">
         <v>10.0</v>
@@ -1385,7 +1385,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I15" s="3">
         <v>20.0</v>
@@ -1393,8 +1393,8 @@
       <c r="J15" s="3">
         <v>0.0</v>
       </c>
-      <c r="K15" s="1">
-        <v>3.0</v>
+      <c r="K15" s="3">
+        <v>0.0</v>
       </c>
       <c r="L15" s="3">
         <v>16.0</v>
@@ -1402,8 +1402,8 @@
       <c r="M15" s="1">
         <v>3.0</v>
       </c>
-      <c r="N15" s="1">
-        <v>6.0</v>
+      <c r="N15" s="3">
+        <v>3.0</v>
       </c>
       <c r="O15" s="1">
         <v>10.0</v>
@@ -1438,7 +1438,7 @@
         <v>0.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I16" s="3">
         <v>25.0</v>
@@ -1446,8 +1446,8 @@
       <c r="J16" s="3">
         <v>0.0</v>
       </c>
-      <c r="K16" s="1">
-        <v>3.0</v>
+      <c r="K16" s="3">
+        <v>0.0</v>
       </c>
       <c r="L16" s="3">
         <v>20.0</v>
@@ -1455,8 +1455,8 @@
       <c r="M16" s="1">
         <v>3.0</v>
       </c>
-      <c r="N16" s="1">
-        <v>6.0</v>
+      <c r="N16" s="3">
+        <v>3.0</v>
       </c>
       <c r="O16" s="1">
         <v>10.0</v>
@@ -1491,7 +1491,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I17" s="3">
         <v>30.0</v>
@@ -1499,8 +1499,8 @@
       <c r="J17" s="3">
         <v>0.0</v>
       </c>
-      <c r="K17" s="1">
-        <v>3.0</v>
+      <c r="K17" s="3">
+        <v>0.0</v>
       </c>
       <c r="L17" s="3">
         <v>24.0</v>
@@ -1508,8 +1508,8 @@
       <c r="M17" s="1">
         <v>3.0</v>
       </c>
-      <c r="N17" s="1">
-        <v>6.0</v>
+      <c r="N17" s="3">
+        <v>3.0</v>
       </c>
       <c r="O17" s="1">
         <v>10.0</v>
@@ -1544,7 +1544,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I18" s="3">
         <v>35.0</v>
@@ -1552,8 +1552,8 @@
       <c r="J18" s="3">
         <v>0.0</v>
       </c>
-      <c r="K18" s="1">
-        <v>3.0</v>
+      <c r="K18" s="3">
+        <v>0.0</v>
       </c>
       <c r="L18" s="3">
         <v>28.0</v>
@@ -1561,8 +1561,8 @@
       <c r="M18" s="1">
         <v>3.0</v>
       </c>
-      <c r="N18" s="1">
-        <v>6.0</v>
+      <c r="N18" s="3">
+        <v>3.0</v>
       </c>
       <c r="O18" s="1">
         <v>10.0</v>
@@ -1597,7 +1597,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I19" s="3">
         <v>40.0</v>
@@ -1605,8 +1605,8 @@
       <c r="J19" s="3">
         <v>0.0</v>
       </c>
-      <c r="K19" s="1">
-        <v>3.0</v>
+      <c r="K19" s="3">
+        <v>0.0</v>
       </c>
       <c r="L19" s="3">
         <v>32.0</v>
@@ -1614,8 +1614,8 @@
       <c r="M19" s="1">
         <v>3.0</v>
       </c>
-      <c r="N19" s="1">
-        <v>6.0</v>
+      <c r="N19" s="3">
+        <v>3.0</v>
       </c>
       <c r="O19" s="1">
         <v>10.0</v>
@@ -1703,7 +1703,7 @@
         <v>0.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I21" s="3">
         <v>10.0</v>
@@ -1757,7 +1757,7 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I22" s="3">
         <v>7.5</v>
@@ -1810,7 +1810,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I23" s="3">
         <v>10.0</v>
@@ -1863,7 +1863,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I24" s="3">
         <v>12.5</v>
@@ -1916,7 +1916,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I25" s="3">
         <v>15.0</v>
@@ -1969,7 +1969,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I26" s="3">
         <v>17.5</v>
@@ -2022,7 +2022,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I27" s="3">
         <v>20.0</v>
@@ -2167,7 +2167,7 @@
         <v>6.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
@@ -2184,7 +2184,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I30" s="1">
         <v>5.0</v>
@@ -2220,7 +2220,7 @@
         <v>6.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
@@ -2237,7 +2237,7 @@
         <v>3.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I31" s="1">
         <v>5.0</v>
@@ -2273,7 +2273,7 @@
         <v>6.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32">
@@ -2290,7 +2290,7 @@
         <v>6.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I32" s="1">
         <v>5.0</v>
@@ -2326,7 +2326,7 @@
         <v>6.0</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
@@ -2343,7 +2343,7 @@
         <v>9.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I33" s="1">
         <v>5.0</v>
@@ -2379,7 +2379,7 @@
         <v>6.0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
@@ -2667,7 +2667,7 @@
         <v>93</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F39" s="1">
         <v>8.0</v>
@@ -2676,7 +2676,7 @@
         <v>0.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I39" s="1">
         <v>5.0</v>
@@ -2713,7 +2713,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
@@ -2727,7 +2727,7 @@
         <v>10.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I40" s="1">
         <v>10.0</v>
@@ -2764,7 +2764,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
@@ -2778,7 +2778,7 @@
         <v>15.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I41" s="1">
         <v>7.5</v>
@@ -2815,7 +2815,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
@@ -2829,7 +2829,7 @@
         <v>20.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I42" s="1">
         <v>10.0</v>
@@ -2866,7 +2866,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
@@ -2880,7 +2880,7 @@
         <v>25.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I43" s="1">
         <v>12.5</v>
@@ -2917,7 +2917,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44">
@@ -2931,7 +2931,7 @@
         <v>30.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I44" s="1">
         <v>15.0</v>
@@ -2968,7 +2968,7 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45">
@@ -2982,7 +2982,7 @@
         <v>35.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I45" s="1">
         <v>17.5</v>
@@ -3019,7 +3019,7 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
@@ -3033,7 +3033,7 @@
         <v>40.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I46" s="1">
         <v>20.0</v>
@@ -3070,7 +3070,7 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47">
@@ -3084,7 +3084,7 @@
         <v>45.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I47" s="1">
         <v>22.5</v>
@@ -3121,7 +3121,7 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
@@ -3135,7 +3135,7 @@
         <v>50.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I48" s="1">
         <v>25.0</v>
@@ -3172,7 +3172,7 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49">
@@ -3180,7 +3180,7 @@
         <v>94</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3189,7 +3189,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3225,7 +3225,7 @@
         <v>3.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50">
@@ -3239,7 +3239,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3275,7 +3275,7 @@
         <v>3.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51">
@@ -3289,7 +3289,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3325,7 +3325,7 @@
         <v>3.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
@@ -3339,7 +3339,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3375,7 +3375,7 @@
         <v>3.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53">
@@ -3389,7 +3389,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3425,7 +3425,7 @@
         <v>3.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54">
@@ -3439,7 +3439,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3475,7 +3475,7 @@
         <v>3.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="55">
@@ -3489,7 +3489,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3525,7 +3525,7 @@
         <v>3.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56">
@@ -3539,7 +3539,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3575,7 +3575,7 @@
         <v>3.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57">
@@ -3589,7 +3589,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3625,7 +3625,7 @@
         <v>3.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58">
@@ -3639,7 +3639,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3675,7 +3675,7 @@
         <v>3.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59">
@@ -3683,7 +3683,7 @@
         <v>95</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3692,7 +3692,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3728,7 +3728,7 @@
         <v>18.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60">
@@ -3742,7 +3742,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3778,7 +3778,7 @@
         <v>18.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61">
@@ -3792,7 +3792,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3828,7 +3828,7 @@
         <v>18.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62">
@@ -3842,7 +3842,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3878,7 +3878,7 @@
         <v>18.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63">
@@ -3892,7 +3892,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3928,7 +3928,7 @@
         <v>18.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64">
@@ -3942,7 +3942,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -3978,7 +3978,7 @@
         <v>18.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">
@@ -3992,7 +3992,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4028,7 +4028,7 @@
         <v>18.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66">
@@ -4042,7 +4042,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4078,7 +4078,7 @@
         <v>18.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67">
@@ -4092,7 +4092,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4128,7 +4128,7 @@
         <v>18.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68">
@@ -4142,7 +4142,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4178,7 +4178,7 @@
         <v>18.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4206,23 +4206,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5247,15 +5247,15 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
@@ -5263,15 +5263,15 @@
         <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
@@ -5284,10 +5284,10 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -5311,7 +5311,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
@@ -5324,10 +5324,10 @@
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -5335,7 +5335,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
@@ -5343,7 +5343,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
@@ -5351,7 +5351,7 @@
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
@@ -5359,7 +5359,7 @@
         <v>27</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
@@ -5367,31 +5367,31 @@
         <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
@@ -5399,7 +5399,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
@@ -5412,10 +5412,10 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -18,111 +18,132 @@
     <t>Setting</t>
   </si>
   <si>
+    <t>Project</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
-    <t>Project</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
     <t>Company Name</t>
   </si>
   <si>
+    <t>BUA</t>
+  </si>
+  <si>
     <t>Alahly Sabbour</t>
   </si>
   <si>
-    <t/>
+    <t>Phase</t>
   </si>
   <si>
     <t>Currency</t>
   </si>
   <si>
+    <t>Plan</t>
+  </si>
+  <si>
     <t>EGP</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
-    <t>BUA</t>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Discount %</t>
   </si>
   <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Plan</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
     <t>Down Payment Type</t>
   </si>
   <si>
+    <t>Down Payment 1 %</t>
+  </si>
+  <si>
+    <t>Down Payment 2 %</t>
+  </si>
+  <si>
+    <t>DP2 Due (months)</t>
+  </si>
+  <si>
     <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
+    <t>Installments Count</t>
+  </si>
+  <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
+    <t>Installment Every (months)</t>
+  </si>
+  <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
-    <t>Down Payment 1 %</t>
+    <t>First Installment Due (months)</t>
   </si>
   <si>
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
-    <t>Down Payment 2 %</t>
-  </si>
-  <si>
-    <t>DP2 Due (months)</t>
+    <t>Maintenance %</t>
+  </si>
+  <si>
+    <t>Delivery (months)</t>
+  </si>
+  <si>
+    <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
     <t>Column</t>
   </si>
   <si>
+    <t>Ending Installment Maintenance Due (months)</t>
+  </si>
+  <si>
     <t>Meaning / المعنى</t>
   </si>
   <si>
-    <t>Installments Count</t>
+    <t>Maintenance Basis</t>
   </si>
   <si>
     <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
-    <t>Installment Every (months)</t>
-  </si>
-  <si>
-    <t>First Installment Due (months)</t>
+    <t>YOUD</t>
+  </si>
+  <si>
+    <t>YOUD &amp; YOUD EL BAHR</t>
   </si>
   <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
-    <t>Maintenance %</t>
-  </si>
-  <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
-    <t>Delivery (months)</t>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
     <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
+    <t>Original Price</t>
+  </si>
+  <si>
     <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
   </si>
   <si>
@@ -132,39 +153,21 @@
     <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
   </si>
   <si>
-    <t>First Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>Number of equal installments / عدد الأقساط</t>
   </si>
   <si>
-    <t>Ending Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
   </si>
   <si>
-    <t>Maintenance Basis</t>
-  </si>
-  <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
   </si>
   <si>
-    <t>YOUD &amp; YOUD EL BAHR</t>
-  </si>
-  <si>
     <t>Admin Fee %</t>
   </si>
   <si>
     <t>% of system price, paid upfront / رسوم إدارية</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
     <t>Operations Fee %</t>
   </si>
   <si>
@@ -174,21 +177,18 @@
     <t>% of system price, due at delivery / وديعة الصيانة</t>
   </si>
   <si>
-    <t>Original Price</t>
-  </si>
-  <si>
     <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
   </si>
   <si>
+    <t>Selling price</t>
+  </si>
+  <si>
     <t>After editing: save the file, then refresh the page in the browser.</t>
   </si>
   <si>
     <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
   </si>
   <si>
-    <t>Selling price</t>
-  </si>
-  <si>
     <t>10% DP &amp; 8 Years</t>
   </si>
   <si>
@@ -240,7 +240,7 @@
     <t>35% DP over 7 years</t>
   </si>
   <si>
-    <t>20% DP &amp; 20% After 3 months over 8 years</t>
+    <t>40% DP over 8 years</t>
   </si>
   <si>
     <t>Cash discount 15%</t>
@@ -600,75 +600,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -715,12 +715,12 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>58</v>
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -770,12 +770,12 @@
         <v>6.0</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>59</v>
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -825,12 +825,12 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>60</v>
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -879,12 +879,12 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>61</v>
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -933,12 +933,12 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>62</v>
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -987,12 +987,12 @@
         <v>6.0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>63</v>
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1041,12 +1041,12 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>64</v>
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1095,12 +1095,12 @@
         <v>6.0</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>65</v>
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1149,12 +1149,12 @@
         <v>6.0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>66</v>
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1205,12 +1205,12 @@
         <v>6.0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1262,7 +1262,7 @@
         <v>6.0</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I13" s="1">
         <v>10.0</v>
@@ -1315,7 +1315,7 @@
         <v>3.0</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I14" s="3">
         <v>15.0</v>
@@ -1368,7 +1368,7 @@
         <v>3.0</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -1385,7 +1385,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I15" s="3">
         <v>20.0</v>
@@ -1421,7 +1421,7 @@
         <v>3.0</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -1438,7 +1438,7 @@
         <v>0.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I16" s="3">
         <v>25.0</v>
@@ -1474,7 +1474,7 @@
         <v>3.0</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
@@ -1491,7 +1491,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I17" s="3">
         <v>30.0</v>
@@ -1527,7 +1527,7 @@
         <v>3.0</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I18" s="3">
         <v>35.0</v>
@@ -1580,14 +1580,14 @@
         <v>3.0</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F19" s="1">
@@ -1597,7 +1597,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I19" s="3">
         <v>40.0</v>
@@ -1633,7 +1633,7 @@
         <v>3.0</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
@@ -1650,7 +1650,7 @@
         <v>15.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I20" s="1">
         <v>100.0</v>
@@ -1686,7 +1686,7 @@
         <v>3.0</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
@@ -1703,7 +1703,7 @@
         <v>0.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I21" s="3">
         <v>10.0</v>
@@ -1740,7 +1740,7 @@
         <v>3.0</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22">
@@ -1757,7 +1757,7 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I22" s="3">
         <v>7.5</v>
@@ -1793,7 +1793,7 @@
         <v>3.0</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -1810,7 +1810,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I23" s="3">
         <v>10.0</v>
@@ -1846,7 +1846,7 @@
         <v>3.0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
@@ -1863,7 +1863,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I24" s="3">
         <v>12.5</v>
@@ -1899,7 +1899,7 @@
         <v>3.0</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
@@ -1916,7 +1916,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I25" s="3">
         <v>15.0</v>
@@ -1952,7 +1952,7 @@
         <v>3.0</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -1969,7 +1969,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I26" s="3">
         <v>17.5</v>
@@ -2005,7 +2005,7 @@
         <v>3.0</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
@@ -2022,7 +2022,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I27" s="3">
         <v>20.0</v>
@@ -2058,7 +2058,7 @@
         <v>3.0</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
@@ -2075,7 +2075,7 @@
         <v>15.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I28" s="3">
         <v>100.0</v>
@@ -2111,7 +2111,7 @@
         <v>3.0</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
@@ -2131,7 +2131,7 @@
         <v>25.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I29" s="1">
         <v>100.0</v>
@@ -2167,7 +2167,7 @@
         <v>6.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
@@ -2184,7 +2184,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I30" s="1">
         <v>5.0</v>
@@ -2220,7 +2220,7 @@
         <v>6.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31">
@@ -2237,7 +2237,7 @@
         <v>3.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I31" s="1">
         <v>5.0</v>
@@ -2273,7 +2273,7 @@
         <v>6.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
@@ -2290,7 +2290,7 @@
         <v>6.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I32" s="1">
         <v>5.0</v>
@@ -2326,7 +2326,7 @@
         <v>6.0</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33">
@@ -2343,7 +2343,7 @@
         <v>9.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I33" s="1">
         <v>5.0</v>
@@ -2379,7 +2379,7 @@
         <v>6.0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34">
@@ -2399,7 +2399,7 @@
         <v>25.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I34" s="1">
         <v>100.0</v>
@@ -2435,7 +2435,7 @@
         <v>6.0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
@@ -2455,7 +2455,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I35" s="1">
         <v>5.0</v>
@@ -2491,7 +2491,7 @@
         <v>6.0</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
@@ -2511,7 +2511,7 @@
         <v>3.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I36" s="1">
         <v>5.0</v>
@@ -2547,7 +2547,7 @@
         <v>6.0</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37">
@@ -2567,7 +2567,7 @@
         <v>6.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I37" s="1">
         <v>5.0</v>
@@ -2603,7 +2603,7 @@
         <v>6.0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38">
@@ -2623,7 +2623,7 @@
         <v>9.0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I38" s="1">
         <v>5.0</v>
@@ -2659,7 +2659,7 @@
         <v>6.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39">
@@ -2667,7 +2667,7 @@
         <v>93</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F39" s="1">
         <v>8.0</v>
@@ -2676,7 +2676,7 @@
         <v>0.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I39" s="1">
         <v>5.0</v>
@@ -2713,7 +2713,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
@@ -2727,7 +2727,7 @@
         <v>10.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I40" s="1">
         <v>10.0</v>
@@ -2764,7 +2764,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -2778,7 +2778,7 @@
         <v>15.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I41" s="1">
         <v>7.5</v>
@@ -2815,7 +2815,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
@@ -2829,7 +2829,7 @@
         <v>20.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I42" s="1">
         <v>10.0</v>
@@ -2866,7 +2866,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -2880,7 +2880,7 @@
         <v>25.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I43" s="1">
         <v>12.5</v>
@@ -2917,7 +2917,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
@@ -2931,7 +2931,7 @@
         <v>30.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I44" s="1">
         <v>15.0</v>
@@ -2968,7 +2968,7 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45">
@@ -2982,7 +2982,7 @@
         <v>35.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I45" s="1">
         <v>17.5</v>
@@ -3019,7 +3019,7 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
@@ -3033,7 +3033,7 @@
         <v>40.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I46" s="1">
         <v>20.0</v>
@@ -3070,7 +3070,7 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47">
@@ -3084,7 +3084,7 @@
         <v>45.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I47" s="1">
         <v>22.5</v>
@@ -3121,7 +3121,7 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
@@ -3135,7 +3135,7 @@
         <v>50.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I48" s="1">
         <v>25.0</v>
@@ -3172,7 +3172,7 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49">
@@ -3180,7 +3180,7 @@
         <v>94</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3189,7 +3189,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3225,7 +3225,7 @@
         <v>3.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50">
@@ -3239,7 +3239,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3275,7 +3275,7 @@
         <v>3.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51">
@@ -3289,7 +3289,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3325,7 +3325,7 @@
         <v>3.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
@@ -3339,7 +3339,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3375,7 +3375,7 @@
         <v>3.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
@@ -3389,7 +3389,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3425,7 +3425,7 @@
         <v>3.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
@@ -3439,7 +3439,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3475,7 +3475,7 @@
         <v>3.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55">
@@ -3489,7 +3489,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3525,7 +3525,7 @@
         <v>3.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56">
@@ -3539,7 +3539,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3575,7 +3575,7 @@
         <v>3.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57">
@@ -3589,7 +3589,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3625,7 +3625,7 @@
         <v>3.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58">
@@ -3639,7 +3639,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3675,7 +3675,7 @@
         <v>3.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59">
@@ -3683,7 +3683,7 @@
         <v>95</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3692,7 +3692,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3728,7 +3728,7 @@
         <v>18.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60">
@@ -3742,7 +3742,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3778,7 +3778,7 @@
         <v>18.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61">
@@ -3792,7 +3792,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3828,7 +3828,7 @@
         <v>18.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62">
@@ -3842,7 +3842,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3878,7 +3878,7 @@
         <v>18.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63">
@@ -3892,7 +3892,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3928,7 +3928,7 @@
         <v>18.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
@@ -3942,7 +3942,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -3978,7 +3978,7 @@
         <v>18.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65">
@@ -3992,7 +3992,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4028,7 +4028,7 @@
         <v>18.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
@@ -4042,7 +4042,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4078,7 +4078,7 @@
         <v>18.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67">
@@ -4092,7 +4092,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4128,7 +4128,7 @@
         <v>18.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68">
@@ -4142,7 +4142,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4178,7 +4178,7 @@
         <v>18.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -4211,18 +4211,18 @@
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5244,167 +5244,167 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>54</v>
@@ -5412,18 +5412,18 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,60 +15,60 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="96">
   <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Setting</t>
   </si>
   <si>
-    <t>Project</t>
-  </si>
-  <si>
-    <t>How to fill the Projects sheet</t>
+    <t>BUA</t>
+  </si>
+  <si>
+    <t>Phase</t>
   </si>
   <si>
     <t>Value</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Type</t>
+    <t>Plan</t>
   </si>
   <si>
     <t>Company Name</t>
   </si>
   <si>
-    <t>BUA</t>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
     <t>Alahly Sabbour</t>
   </si>
   <si>
-    <t>Phase</t>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Discount %</t>
   </si>
   <si>
     <t>Currency</t>
   </si>
   <si>
-    <t>Plan</t>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
   </si>
   <si>
     <t>EGP</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
@@ -120,30 +120,30 @@
     <t>Maintenance Basis</t>
   </si>
   <si>
+    <t>YOUD</t>
+  </si>
+  <si>
     <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>YOUD &amp; YOUD EL BAHR</t>
   </si>
   <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
+    <t>Original Price</t>
   </si>
   <si>
     <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
-    <t>Original Price</t>
-  </si>
-  <si>
     <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
   </si>
   <si>
@@ -180,13 +180,13 @@
     <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
   </si>
   <si>
+    <t>After editing: save the file, then refresh the page in the browser.</t>
+  </si>
+  <si>
+    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
+  </si>
+  <si>
     <t>Selling price</t>
-  </si>
-  <si>
-    <t>After editing: save the file, then refresh the page in the browser.</t>
-  </si>
-  <si>
-    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
   </si>
   <si>
     <t>10% DP &amp; 8 Years</t>
@@ -600,28 +600,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>18</v>
@@ -662,13 +662,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>37</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -715,7 +715,7 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -770,7 +770,7 @@
         <v>6.0</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -825,7 +825,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5">
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -879,7 +879,7 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -933,7 +933,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -987,7 +987,7 @@
         <v>6.0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1041,7 +1041,7 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1095,7 +1095,7 @@
         <v>6.0</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1149,7 +1149,7 @@
         <v>6.0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1205,7 +1205,7 @@
         <v>6.0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1262,7 +1262,7 @@
         <v>6.0</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I13" s="1">
         <v>10.0</v>
@@ -1315,7 +1315,7 @@
         <v>3.0</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14">
@@ -1332,7 +1332,7 @@
         <v>0.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I14" s="3">
         <v>15.0</v>
@@ -1368,7 +1368,7 @@
         <v>3.0</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -1385,7 +1385,7 @@
         <v>0.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I15" s="3">
         <v>20.0</v>
@@ -1421,7 +1421,7 @@
         <v>3.0</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
@@ -1438,7 +1438,7 @@
         <v>0.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I16" s="3">
         <v>25.0</v>
@@ -1474,7 +1474,7 @@
         <v>3.0</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17">
@@ -1491,7 +1491,7 @@
         <v>0.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I17" s="3">
         <v>30.0</v>
@@ -1527,7 +1527,7 @@
         <v>3.0</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I18" s="3">
         <v>35.0</v>
@@ -1580,7 +1580,7 @@
         <v>3.0</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -1597,7 +1597,7 @@
         <v>0.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I19" s="3">
         <v>40.0</v>
@@ -1633,7 +1633,7 @@
         <v>3.0</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -1650,7 +1650,7 @@
         <v>15.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I20" s="1">
         <v>100.0</v>
@@ -1686,7 +1686,7 @@
         <v>3.0</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21">
@@ -1703,7 +1703,7 @@
         <v>0.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I21" s="3">
         <v>10.0</v>
@@ -1740,7 +1740,7 @@
         <v>3.0</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
@@ -1757,7 +1757,7 @@
         <v>0.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I22" s="3">
         <v>7.5</v>
@@ -1793,7 +1793,7 @@
         <v>3.0</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
@@ -1810,7 +1810,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I23" s="3">
         <v>10.0</v>
@@ -1846,7 +1846,7 @@
         <v>3.0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -1863,7 +1863,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I24" s="3">
         <v>12.5</v>
@@ -1899,7 +1899,7 @@
         <v>3.0</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
@@ -1916,7 +1916,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I25" s="3">
         <v>15.0</v>
@@ -1952,7 +1952,7 @@
         <v>3.0</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26">
@@ -1969,7 +1969,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I26" s="3">
         <v>17.5</v>
@@ -2005,7 +2005,7 @@
         <v>3.0</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
@@ -2022,7 +2022,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I27" s="3">
         <v>20.0</v>
@@ -2058,7 +2058,7 @@
         <v>3.0</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -2075,7 +2075,7 @@
         <v>15.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I28" s="3">
         <v>100.0</v>
@@ -2111,7 +2111,7 @@
         <v>3.0</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29">
@@ -2131,7 +2131,7 @@
         <v>25.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I29" s="1">
         <v>100.0</v>
@@ -2167,7 +2167,7 @@
         <v>6.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
@@ -2184,7 +2184,7 @@
         <v>0.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I30" s="1">
         <v>5.0</v>
@@ -2220,7 +2220,7 @@
         <v>6.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
@@ -2237,7 +2237,7 @@
         <v>3.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I31" s="1">
         <v>5.0</v>
@@ -2273,7 +2273,7 @@
         <v>6.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
@@ -2290,7 +2290,7 @@
         <v>6.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I32" s="1">
         <v>5.0</v>
@@ -2326,7 +2326,7 @@
         <v>6.0</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -2343,7 +2343,7 @@
         <v>9.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I33" s="1">
         <v>5.0</v>
@@ -2379,7 +2379,7 @@
         <v>6.0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
@@ -2399,7 +2399,7 @@
         <v>25.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I34" s="1">
         <v>100.0</v>
@@ -2435,7 +2435,7 @@
         <v>6.0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35">
@@ -2455,7 +2455,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I35" s="1">
         <v>5.0</v>
@@ -2491,7 +2491,7 @@
         <v>6.0</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
@@ -2511,7 +2511,7 @@
         <v>3.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I36" s="1">
         <v>5.0</v>
@@ -2547,7 +2547,7 @@
         <v>6.0</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
@@ -2567,7 +2567,7 @@
         <v>6.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I37" s="1">
         <v>5.0</v>
@@ -2603,7 +2603,7 @@
         <v>6.0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
@@ -2623,7 +2623,7 @@
         <v>9.0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I38" s="1">
         <v>5.0</v>
@@ -2659,7 +2659,7 @@
         <v>6.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
@@ -2667,7 +2667,7 @@
         <v>93</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F39" s="1">
         <v>8.0</v>
@@ -2676,7 +2676,7 @@
         <v>0.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I39" s="1">
         <v>5.0</v>
@@ -2713,7 +2713,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -2727,7 +2727,7 @@
         <v>10.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I40" s="1">
         <v>10.0</v>
@@ -2764,7 +2764,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -2778,7 +2778,7 @@
         <v>15.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I41" s="1">
         <v>7.5</v>
@@ -2815,7 +2815,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -2829,7 +2829,7 @@
         <v>20.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I42" s="1">
         <v>10.0</v>
@@ -2866,7 +2866,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -2880,7 +2880,7 @@
         <v>25.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I43" s="1">
         <v>12.5</v>
@@ -2917,7 +2917,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -2931,7 +2931,7 @@
         <v>30.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I44" s="1">
         <v>15.0</v>
@@ -2968,7 +2968,7 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45">
@@ -2982,7 +2982,7 @@
         <v>35.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I45" s="1">
         <v>17.5</v>
@@ -3019,7 +3019,7 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46">
@@ -3033,7 +3033,7 @@
         <v>40.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I46" s="1">
         <v>20.0</v>
@@ -3070,7 +3070,7 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47">
@@ -3084,7 +3084,7 @@
         <v>45.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I47" s="1">
         <v>22.5</v>
@@ -3121,7 +3121,7 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48">
@@ -3135,7 +3135,7 @@
         <v>50.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I48" s="1">
         <v>25.0</v>
@@ -3172,7 +3172,7 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49">
@@ -3180,7 +3180,7 @@
         <v>94</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3189,7 +3189,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3225,7 +3225,7 @@
         <v>3.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
@@ -3239,7 +3239,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3275,7 +3275,7 @@
         <v>3.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
@@ -3289,7 +3289,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3325,7 +3325,7 @@
         <v>3.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
@@ -3339,7 +3339,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3375,7 +3375,7 @@
         <v>3.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53">
@@ -3389,7 +3389,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3425,7 +3425,7 @@
         <v>3.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54">
@@ -3439,7 +3439,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3475,7 +3475,7 @@
         <v>3.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
@@ -3489,7 +3489,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3525,7 +3525,7 @@
         <v>3.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56">
@@ -3539,7 +3539,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3575,7 +3575,7 @@
         <v>3.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
@@ -3589,7 +3589,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3625,7 +3625,7 @@
         <v>3.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
@@ -3639,7 +3639,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3675,7 +3675,7 @@
         <v>3.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59">
@@ -3683,7 +3683,7 @@
         <v>95</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3692,7 +3692,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3728,7 +3728,7 @@
         <v>18.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60">
@@ -3742,7 +3742,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3778,7 +3778,7 @@
         <v>18.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
@@ -3792,7 +3792,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3828,7 +3828,7 @@
         <v>18.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
@@ -3842,7 +3842,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3878,7 +3878,7 @@
         <v>18.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
@@ -3892,7 +3892,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3928,7 +3928,7 @@
         <v>18.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
@@ -3942,7 +3942,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -3978,7 +3978,7 @@
         <v>18.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -3992,7 +3992,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4028,7 +4028,7 @@
         <v>18.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
@@ -4042,7 +4042,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4078,7 +4078,7 @@
         <v>18.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -4092,7 +4092,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4128,7 +4128,7 @@
         <v>18.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68">
@@ -4142,7 +4142,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4178,7 +4178,7 @@
         <v>18.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -4203,26 +4203,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5244,26 +5244,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
@@ -5284,10 +5284,10 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -5300,15 +5300,15 @@
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>38</v>
@@ -5316,18 +5316,18 @@
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -5412,18 +5412,18 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -13,134 +13,167 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="96">
   <si>
     <t>Project</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>BUA</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Down Payment Type</t>
+  </si>
+  <si>
+    <t>Down Payment 1 %</t>
+  </si>
+  <si>
+    <t>Down Payment 2 %</t>
+  </si>
+  <si>
+    <t>DP2 Due (months)</t>
+  </si>
+  <si>
+    <t>Installments Count</t>
+  </si>
+  <si>
+    <t>Installment Every (months)</t>
+  </si>
+  <si>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance %</t>
+  </si>
+  <si>
+    <t>Delivery (months)</t>
+  </si>
+  <si>
+    <t>First Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Ending Installment Maintenance Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance Basis</t>
+  </si>
+  <si>
+    <t>YOUD</t>
+  </si>
+  <si>
+    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>Original Price</t>
+  </si>
+  <si>
+    <t>Selling price</t>
+  </si>
+  <si>
+    <t>10% DP &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>7.5% DP &amp; 7.5% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>10% DP &amp; 10% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>12.5% DP &amp; 12.5% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>15% DP &amp; 15% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>17.5% DP &amp; 17.5% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>20% DP &amp; 20% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>22.5% DP &amp; 22.5% After 3 Months &amp; 8 Years</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>25% DP &amp; 25% After 3 Months No Years</t>
+  </si>
+  <si>
+    <t>YOUD EL BAHR</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
-    <t>Type</t>
+    <t>EGP</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>BUA</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Plan</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
     <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
-    <t>Alahly Sabbour</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Discount %</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
-    <t>Down Payment Type</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>Down Payment 1 %</t>
-  </si>
-  <si>
-    <t>Down Payment 2 %</t>
-  </si>
-  <si>
-    <t>DP2 Due (months)</t>
-  </si>
-  <si>
     <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
-    <t>Installments Count</t>
-  </si>
-  <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
-    <t>Installment Every (months)</t>
-  </si>
-  <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
-    <t>First Installment Due (months)</t>
-  </si>
-  <si>
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
-    <t>Maintenance %</t>
-  </si>
-  <si>
-    <t>Delivery (months)</t>
-  </si>
-  <si>
-    <t>First Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>Column</t>
   </si>
   <si>
-    <t>Ending Installment Maintenance Due (months)</t>
-  </si>
-  <si>
     <t>Meaning / المعنى</t>
   </si>
   <si>
-    <t>Maintenance Basis</t>
-  </si>
-  <si>
-    <t>YOUD</t>
-  </si>
-  <si>
     <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
-    <t>YOUD &amp; YOUD EL BAHR</t>
-  </si>
-  <si>
     <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
   </si>
   <si>
-    <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
     <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
-    <t>Original Price</t>
-  </si>
-  <si>
     <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
@@ -184,39 +217,6 @@
   </si>
   <si>
     <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
-  </si>
-  <si>
-    <t>Selling price</t>
-  </si>
-  <si>
-    <t>10% DP &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>7.5% DP &amp; 7.5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>10% DP &amp; 10% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>12.5% DP &amp; 12.5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>15% DP &amp; 15% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>17.5% DP &amp; 17.5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>20% DP &amp; 20% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>22.5% DP &amp; 22.5% After 3 Months &amp; 8 Years</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>25% DP &amp; 25% After 3 Months No Years</t>
   </si>
   <si>
     <t>RTM</t>
@@ -603,72 +603,72 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>37</v>
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -701,29 +701,29 @@
         <v>10.0</v>
       </c>
       <c r="P2" s="1">
-        <f>4*12</f>
+        <f t="shared" ref="P2:P4" si="1">4*12</f>
         <v>48</v>
       </c>
       <c r="Q2" s="1">
         <v>30.0</v>
       </c>
       <c r="R2" s="1">
-        <f t="shared" ref="R2:R10" si="1">P2-6</f>
+        <f t="shared" ref="R2:R10" si="2">P2-6</f>
         <v>42</v>
       </c>
       <c r="S2" s="1">
         <v>6.0</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="3" t="s">
-        <v>37</v>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1">
         <v>8.0</v>
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -756,29 +756,29 @@
         <v>10.0</v>
       </c>
       <c r="P3" s="1">
-        <f t="shared" ref="P3:P4" si="2">12*4</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="Q3" s="1">
         <v>30.0</v>
       </c>
       <c r="R3" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="S3" s="1">
         <v>6.0</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="3" t="s">
-        <v>37</v>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1">
         <v>8.0</v>
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -811,29 +811,29 @@
         <v>10.0</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="Q4" s="1">
         <v>30.0</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>42</v>
       </c>
       <c r="S4" s="1">
         <v>6.0</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="s">
-        <v>37</v>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F5" s="1">
         <v>8.0</v>
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -865,29 +865,29 @@
       <c r="O5" s="1">
         <v>10.0</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="2">
         <v>18.0</v>
       </c>
       <c r="R5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="S5" s="1">
         <v>6.0</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="s">
-        <v>37</v>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="F6" s="1">
         <v>8.0</v>
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -919,29 +919,29 @@
       <c r="O6" s="1">
         <v>10.0</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="2">
         <v>18.0</v>
       </c>
       <c r="R6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="S6" s="1">
         <v>6.0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="s">
-        <v>37</v>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="F7" s="1">
         <v>8.0</v>
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -973,29 +973,29 @@
       <c r="O7" s="1">
         <v>10.0</v>
       </c>
-      <c r="P7" s="1">
+      <c r="P7" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q7" s="1">
+      <c r="Q7" s="2">
         <v>18.0</v>
       </c>
       <c r="R7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="S7" s="1">
         <v>6.0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="s">
-        <v>37</v>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F8" s="1">
         <v>8.0</v>
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1027,29 +1027,29 @@
       <c r="O8" s="1">
         <v>10.0</v>
       </c>
-      <c r="P8" s="1">
+      <c r="P8" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q8" s="1">
+      <c r="Q8" s="2">
         <v>18.0</v>
       </c>
       <c r="R8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="S8" s="1">
         <v>6.0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="s">
-        <v>37</v>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1">
         <v>8.0</v>
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1081,29 +1081,29 @@
       <c r="O9" s="1">
         <v>10.0</v>
       </c>
-      <c r="P9" s="1">
+      <c r="P9" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q9" s="1">
+      <c r="Q9" s="2">
         <v>18.0</v>
       </c>
       <c r="R9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="S9" s="1">
         <v>6.0</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="s">
-        <v>37</v>
+      <c r="B10" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1">
         <v>8.0</v>
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1135,32 +1135,32 @@
       <c r="O10" s="1">
         <v>10.0</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P10" s="2">
         <v>36.0</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q10" s="2">
         <v>18.0</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="S10" s="1">
         <v>6.0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="s">
-        <v>37</v>
+      <c r="B11" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1">
         <v>0.0</v>
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1195,28 +1195,28 @@
       <c r="P11" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q11" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R11" s="3">
+      <c r="Q11" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R11" s="2">
         <v>18.0</v>
       </c>
       <c r="S11" s="1">
         <v>6.0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="2">
         <v>4.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="F12" s="1">
         <v>0.0</v>
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1255,1536 +1255,1545 @@
         <v>18.0</v>
       </c>
       <c r="R12" s="1">
-        <f>P12-6</f>
+        <f t="shared" ref="R12:R22" si="3">P12-6</f>
         <v>30</v>
       </c>
       <c r="S12" s="1">
         <v>6.0</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="1" t="s">
-        <v>68</v>
+      <c r="B13" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="G13" s="1">
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I13" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="J13" s="1">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K13" s="1">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="L13" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M13" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O13" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P13" s="1">
+        <f t="shared" ref="P13:P22" si="4">4*12</f>
+        <v>48</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R13" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="S13" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="1">
         <v>8.0</v>
       </c>
-      <c r="M13" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N13" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="1">
-        <v>3.0</v>
-      </c>
       <c r="G14" s="1">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I14" s="3">
+        <v>21</v>
+      </c>
+      <c r="I14" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L14" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="M14" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="O14" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P14" s="1">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R14" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="S14" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G15" s="1">
         <v>15.0</v>
       </c>
-      <c r="J14" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0.0</v>
-      </c>
       <c r="H15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I15" s="3">
+        <v>21</v>
+      </c>
+      <c r="I15" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L15" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M15" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O15" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P15" s="1">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R15" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="S15" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G16" s="1">
         <v>20.0</v>
       </c>
-      <c r="J15" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>16.0</v>
-      </c>
-      <c r="M15" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O15" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P15" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R15" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="S15" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.0</v>
-      </c>
       <c r="H16" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I16" s="3">
+        <v>21</v>
+      </c>
+      <c r="I16" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J16" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K16" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L16" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O16" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P16" s="1">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R16" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="S16" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G17" s="1">
         <v>25.0</v>
       </c>
-      <c r="J16" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="M16" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N16" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O16" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P16" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R16" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="S16" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0.0</v>
-      </c>
       <c r="H17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I17" s="3">
+        <v>21</v>
+      </c>
+      <c r="I17" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="J17" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P17" s="1">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="Q17" s="1">
         <v>30.0</v>
       </c>
-      <c r="J17" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>24.0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N17" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O17" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0.0</v>
-      </c>
       <c r="R17" s="1">
-        <v>9.0</v>
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
       <c r="S17" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>74</v>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="F18" s="1">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="3">
-        <v>28.0</v>
+        <v>21</v>
+      </c>
+      <c r="I18" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>31.0</v>
       </c>
       <c r="M18" s="1">
         <v>3.0</v>
       </c>
-      <c r="N18" s="3">
-        <v>3.0</v>
+      <c r="N18" s="1">
+        <v>6.0</v>
       </c>
       <c r="O18" s="1">
         <v>10.0</v>
       </c>
       <c r="P18" s="1">
-        <v>0.0</v>
+        <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="R18" s="1">
-        <v>9.0</v>
+        <f t="shared" si="3"/>
+        <v>42</v>
       </c>
       <c r="S18" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>75</v>
+      <c r="B19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="F19" s="1">
         <v>8.0</v>
       </c>
       <c r="G19" s="1">
-        <v>0.0</v>
+        <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I19" s="3">
+        <v>21</v>
+      </c>
+      <c r="I19" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="J19" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="K19" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O19" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P19" s="1">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R19" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="S19" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G20" s="1">
         <v>40.0</v>
       </c>
-      <c r="J19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="3">
+      <c r="H20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M20" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P20" s="1">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R20" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="S20" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="J21" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M21" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P21" s="1">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R21" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="S21" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="J22" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="K22" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M22" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O22" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P22" s="1">
+        <f t="shared" si="4"/>
+        <v>48</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="R22" s="1">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="S22" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="T22" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="M24" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N24" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O24" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="S24" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="M25" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O25" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="2">
+        <v>25.0</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="M26" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O26" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="S26" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="M27" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O27" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P27" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="S27" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T27" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F28" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>28.0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="S28" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T28" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="2">
         <v>32.0</v>
       </c>
-      <c r="M19" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N19" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O19" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P19" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R19" s="1">
+      <c r="M29" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N29" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R29" s="1">
         <v>9.0</v>
       </c>
-      <c r="S19" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="1" t="s">
+      <c r="S29" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="1">
+      <c r="F30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G30" s="1">
         <v>15.0</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I20" s="1">
+      <c r="H30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="1">
         <v>100.0</v>
       </c>
-      <c r="J20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="R20" s="1">
+      <c r="J30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="Q30" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="R30" s="1">
         <v>9.0</v>
       </c>
-      <c r="S20" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="3" t="s">
+      <c r="S30" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F31" s="2">
         <v>4.0</v>
       </c>
-      <c r="G21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I21" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="1">
+      <c r="G31" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L31" s="1">
         <f>4*4</f>
         <v>16</v>
       </c>
-      <c r="M21" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N21" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="O21" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="M31" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N31" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="O31" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P31" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q21" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="Q31" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R31" s="2">
         <v>15.0</v>
       </c>
-      <c r="S21" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="3" t="s">
+      <c r="S31" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E32" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F32" s="2">
         <v>5.0</v>
       </c>
-      <c r="G22" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="G32" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I32" s="2">
         <v>7.5</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J32" s="2">
         <v>7.5</v>
       </c>
-      <c r="K22" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="K32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L32" s="2">
         <v>19.0</v>
       </c>
-      <c r="M22" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="M32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N32" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O32" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P32" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q22" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="Q32" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R32" s="2">
         <v>15.0</v>
       </c>
-      <c r="S22" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="3" t="s">
+      <c r="S32" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E33" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F23" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I23" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J23" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="F33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="G33" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L33" s="2">
         <v>23.0</v>
       </c>
-      <c r="M23" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N23" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="O23" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="M33" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O33" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P33" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q23" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="Q33" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R33" s="2">
         <v>15.0</v>
       </c>
-      <c r="S23" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="3" t="s">
+      <c r="S33" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E34" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F34" s="2">
         <v>7.0</v>
       </c>
-      <c r="G24" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="G34" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I34" s="2">
         <v>12.5</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J34" s="2">
         <v>12.5</v>
       </c>
-      <c r="K24" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="K34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L34" s="2">
         <v>27.0</v>
       </c>
-      <c r="M24" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="M34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N34" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O34" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P34" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q24" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="Q34" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R34" s="2">
         <v>15.0</v>
       </c>
-      <c r="S24" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="3" t="s">
+      <c r="S34" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E35" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F35" s="2">
         <v>8.0</v>
       </c>
-      <c r="G25" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I25" s="3">
+      <c r="G35" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I35" s="2">
         <v>15.0</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J35" s="2">
         <v>15.0</v>
       </c>
-      <c r="K25" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L25" s="3">
+      <c r="K35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L35" s="2">
         <v>31.0</v>
       </c>
-      <c r="M25" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N25" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="O25" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P25" s="3">
+      <c r="M35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N35" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O35" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P35" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q25" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R25" s="3">
+      <c r="Q35" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R35" s="2">
         <v>15.0</v>
       </c>
-      <c r="S25" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="3" t="s">
+      <c r="S35" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E36" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F36" s="2">
         <v>9.0</v>
       </c>
-      <c r="G26" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="G36" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I36" s="2">
         <v>17.5</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J36" s="2">
         <v>17.5</v>
       </c>
-      <c r="K26" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="K36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L36" s="2">
         <v>35.0</v>
       </c>
-      <c r="M26" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N26" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="O26" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="M36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N36" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O36" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P36" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q26" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="Q36" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R36" s="2">
         <v>15.0</v>
       </c>
-      <c r="S26" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="3" t="s">
+      <c r="S36" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T36" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F27" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="F37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I37" s="2">
         <v>20.0</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J37" s="2">
         <v>20.0</v>
       </c>
-      <c r="K27" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="K37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="L37" s="2">
         <v>39.0</v>
       </c>
-      <c r="M27" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="N27" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="O27" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="M37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="N37" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="O37" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P37" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q27" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="Q37" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R37" s="2">
         <v>15.0</v>
       </c>
-      <c r="S27" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="3" t="s">
+      <c r="S37" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="F38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="G38" s="2">
         <v>15.0</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I28" s="3">
+      <c r="H38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="2">
         <v>100.0</v>
       </c>
-      <c r="J28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O28" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="P28" s="3">
+      <c r="J38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P38" s="2">
         <v>12.0</v>
       </c>
-      <c r="Q28" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R28" s="3">
+      <c r="Q38" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R38" s="2">
         <v>15.0</v>
       </c>
-      <c r="S28" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G29" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I29" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="J29" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="N29" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="O29" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P29" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q29" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R29" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S29" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F30" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I30" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J30" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K30" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L30" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M30" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N30" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O30" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P30" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q30" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R30" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S30" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="G31" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I31" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J31" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K31" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L31" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O31" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R31" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S31" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F32" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="G32" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I32" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K32" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L32" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N32" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O32" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R32" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S32" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="G33" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I33" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J33" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K33" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L33" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N33" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O33" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P33" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="1">
-        <v>25.0</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I34" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="J34" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P34" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R34" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S34" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F35" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I35" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L35" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N35" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O35" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P35" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q35" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R35" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F36" s="1">
-        <v>7.0</v>
-      </c>
-      <c r="G36" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I36" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J36" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K36" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L36" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M36" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N36" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O36" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P36" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R36" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S36" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C37" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F37" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="G37" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I37" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J37" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K37" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L37" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M37" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N37" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O37" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P37" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R37" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S37" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C38" s="4">
-        <v>20000.0</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F38" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="G38" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I38" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J38" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="K38" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L38" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M38" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N38" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O38" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P38" s="1">
-        <v>42.0</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="R38" s="1">
-        <v>39.0</v>
-      </c>
-      <c r="S38" s="1">
-        <v>6.0</v>
+      <c r="S38" s="2">
+        <v>3.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F39" s="1">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G39" s="1">
-        <v>0.0</v>
+        <v>25.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I39" s="1">
-        <v>5.0</v>
+        <v>100.0</v>
       </c>
       <c r="J39" s="1">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="K39" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L39" s="1">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="M39" s="1">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="N39" s="1">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
       <c r="O39" s="1">
         <v>10.0</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" ref="P39:P48" si="3">4*12</f>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q39" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R39" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S39" s="1">
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
+      <c r="B40" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="E40" s="1" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="F40" s="1">
         <v>8.0</v>
       </c>
       <c r="G40" s="1">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I40" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="J40" s="1">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K40" s="1">
         <v>3.0</v>
       </c>
       <c r="L40" s="1">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="M40" s="1">
         <v>3.0</v>
       </c>
       <c r="N40" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="O40" s="1">
         <v>10.0</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q40" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R40" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S40" s="1">
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="E41" s="1" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F41" s="1">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G41" s="1">
-        <v>15.0</v>
+        <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I41" s="1">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="J41" s="1">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="K41" s="1">
         <v>3.0</v>
@@ -2802,40 +2811,42 @@
         <v>10.0</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q41" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R41" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S41" s="1">
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
+      <c r="B42" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="E42" s="1" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F42" s="1">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G42" s="1">
-        <v>20.0</v>
+        <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I42" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="J42" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="K42" s="1">
         <v>3.0</v>
@@ -2853,40 +2864,42 @@
         <v>10.0</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q42" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R42" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S42" s="1">
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
+      <c r="B43" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="E43" s="1" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="F43" s="1">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="G43" s="1">
-        <v>25.0</v>
+        <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I43" s="1">
-        <v>12.5</v>
+        <v>5.0</v>
       </c>
       <c r="J43" s="1">
-        <v>12.5</v>
+        <v>5.0</v>
       </c>
       <c r="K43" s="1">
         <v>3.0</v>
@@ -2904,91 +2917,101 @@
         <v>10.0</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q43" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R43" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S43" s="1">
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
+      <c r="B44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="4">
+        <v>20000.0</v>
+      </c>
       <c r="E44" s="1" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="F44" s="1">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="G44" s="1">
-        <v>30.0</v>
+        <v>25.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I44" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="Q44" s="1">
         <v>15.0</v>
       </c>
-      <c r="J44" s="1">
-        <v>15.0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="L44" s="1">
-        <v>31.0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="O44" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="P44" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>18.0</v>
-      </c>
       <c r="R44" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S44" s="1">
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
+      <c r="B45" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" s="4">
+        <v>20000.0</v>
+      </c>
       <c r="E45" s="1" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F45" s="1">
         <v>8.0</v>
       </c>
       <c r="G45" s="1">
-        <v>35.0</v>
+        <v>0.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I45" s="1">
-        <v>17.5</v>
+        <v>5.0</v>
       </c>
       <c r="J45" s="1">
-        <v>17.5</v>
+        <v>5.0</v>
       </c>
       <c r="K45" s="1">
         <v>3.0</v>
@@ -3006,40 +3029,45 @@
         <v>10.0</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q45" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R45" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S45" s="1">
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
+      <c r="B46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="4">
+        <v>20000.0</v>
+      </c>
       <c r="E46" s="1" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="F46" s="1">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G46" s="1">
-        <v>40.0</v>
+        <v>3.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I46" s="1">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="J46" s="1">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="K46" s="1">
         <v>3.0</v>
@@ -3057,40 +3085,45 @@
         <v>10.0</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q46" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R46" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S46" s="1">
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
+      <c r="B47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="4">
+        <v>20000.0</v>
+      </c>
       <c r="E47" s="1" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F47" s="1">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G47" s="1">
-        <v>45.0</v>
+        <v>6.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I47" s="1">
-        <v>22.5</v>
+        <v>5.0</v>
       </c>
       <c r="J47" s="1">
-        <v>22.5</v>
+        <v>5.0</v>
       </c>
       <c r="K47" s="1">
         <v>3.0</v>
@@ -3108,46 +3141,51 @@
         <v>10.0</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q47" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R47" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S47" s="1">
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
+      <c r="B48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="4">
+        <v>20000.0</v>
+      </c>
       <c r="E48" s="1" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F48" s="1">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="G48" s="1">
-        <v>50.0</v>
+        <v>9.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I48" s="1">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="J48" s="1">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="K48" s="1">
         <v>3.0</v>
       </c>
       <c r="L48" s="1">
-        <v>1.0</v>
+        <v>31.0</v>
       </c>
       <c r="M48" s="1">
         <v>3.0</v>
@@ -3159,28 +3197,27 @@
         <v>10.0</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <v>42.0</v>
       </c>
       <c r="Q48" s="1">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="R48" s="1">
-        <v>48.0</v>
+        <v>39.0</v>
       </c>
       <c r="S48" s="1">
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3189,7 +3226,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3213,24 +3250,25 @@
         <v>10.0</v>
       </c>
       <c r="P49" s="1">
-        <v>24.0</v>
+        <f t="shared" ref="P49:P58" si="5">4*12</f>
+        <v>48</v>
       </c>
       <c r="Q49" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R49" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S49" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="E50" s="1" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F50" s="1">
         <v>8.0</v>
@@ -3239,7 +3277,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3263,24 +3301,25 @@
         <v>10.0</v>
       </c>
       <c r="P50" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q50" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R50" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S50" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="E51" s="1" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F51" s="1">
         <v>8.0</v>
@@ -3289,7 +3328,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3313,24 +3352,25 @@
         <v>10.0</v>
       </c>
       <c r="P51" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q51" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R51" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S51" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="E52" s="1" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F52" s="1">
         <v>8.0</v>
@@ -3339,7 +3379,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3363,24 +3403,25 @@
         <v>10.0</v>
       </c>
       <c r="P52" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q52" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R52" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S52" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53">
       <c r="E53" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="F53" s="1">
         <v>8.0</v>
@@ -3389,7 +3430,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3413,24 +3454,25 @@
         <v>10.0</v>
       </c>
       <c r="P53" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q53" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R53" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S53" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="E54" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="F54" s="1">
         <v>8.0</v>
@@ -3439,7 +3481,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3463,24 +3505,25 @@
         <v>10.0</v>
       </c>
       <c r="P54" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q54" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R54" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S54" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="E55" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F55" s="1">
         <v>8.0</v>
@@ -3489,7 +3532,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3513,24 +3556,25 @@
         <v>10.0</v>
       </c>
       <c r="P55" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q55" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R55" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S55" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="E56" s="1" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="F56" s="1">
         <v>8.0</v>
@@ -3539,7 +3583,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3563,24 +3607,25 @@
         <v>10.0</v>
       </c>
       <c r="P56" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q56" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R56" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S56" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F57" s="1">
         <v>8.0</v>
@@ -3589,7 +3634,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3613,24 +3658,25 @@
         <v>10.0</v>
       </c>
       <c r="P57" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q57" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R57" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S57" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="E58" s="1" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="F58" s="1">
         <v>0.0</v>
@@ -3639,7 +3685,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3663,27 +3709,28 @@
         <v>10.0</v>
       </c>
       <c r="P58" s="1">
-        <v>24.0</v>
+        <f t="shared" si="5"/>
+        <v>48</v>
       </c>
       <c r="Q58" s="1">
-        <v>6.0</v>
+        <v>18.0</v>
       </c>
       <c r="R58" s="1">
-        <v>24.0</v>
+        <v>48.0</v>
       </c>
       <c r="S58" s="1">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="s">
-        <v>95</v>
+      <c r="A59" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3692,7 +3739,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3715,25 +3762,25 @@
       <c r="O59" s="1">
         <v>10.0</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q59" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R59" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S59" s="3">
-        <v>18.0</v>
+      <c r="Q59" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R59" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S59" s="1">
+        <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="1" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="F60" s="1">
         <v>8.0</v>
@@ -3742,7 +3789,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3765,25 +3812,25 @@
       <c r="O60" s="1">
         <v>10.0</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q60" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S60" s="3">
-        <v>18.0</v>
+      <c r="Q60" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S60" s="1">
+        <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="E61" s="1" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F61" s="1">
         <v>8.0</v>
@@ -3792,7 +3839,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3815,25 +3862,25 @@
       <c r="O61" s="1">
         <v>10.0</v>
       </c>
-      <c r="P61" s="3">
+      <c r="P61" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q61" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>18.0</v>
+      <c r="Q61" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R61" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S61" s="1">
+        <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="E62" s="1" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F62" s="1">
         <v>8.0</v>
@@ -3842,7 +3889,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3865,25 +3912,25 @@
       <c r="O62" s="1">
         <v>10.0</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q62" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R62" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S62" s="3">
-        <v>18.0</v>
+      <c r="Q62" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R62" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S62" s="1">
+        <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63">
       <c r="E63" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="F63" s="1">
         <v>8.0</v>
@@ -3892,7 +3939,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3915,25 +3962,25 @@
       <c r="O63" s="1">
         <v>10.0</v>
       </c>
-      <c r="P63" s="3">
+      <c r="P63" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q63" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R63" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S63" s="3">
-        <v>18.0</v>
+      <c r="Q63" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S63" s="1">
+        <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="E64" s="1" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="F64" s="1">
         <v>8.0</v>
@@ -3942,7 +3989,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -3965,25 +4012,25 @@
       <c r="O64" s="1">
         <v>10.0</v>
       </c>
-      <c r="P64" s="3">
+      <c r="P64" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q64" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R64" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S64" s="3">
-        <v>18.0</v>
+      <c r="Q64" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R64" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S64" s="1">
+        <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="E65" s="1" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="F65" s="1">
         <v>8.0</v>
@@ -3992,7 +4039,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4015,25 +4062,25 @@
       <c r="O65" s="1">
         <v>10.0</v>
       </c>
-      <c r="P65" s="3">
+      <c r="P65" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q65" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R65" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S65" s="3">
-        <v>18.0</v>
+      <c r="Q65" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S65" s="1">
+        <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="E66" s="1" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="F66" s="1">
         <v>8.0</v>
@@ -4042,7 +4089,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4065,25 +4112,25 @@
       <c r="O66" s="1">
         <v>10.0</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q66" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R66" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S66" s="3">
-        <v>18.0</v>
+      <c r="Q66" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S66" s="1">
+        <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="E67" s="1" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F67" s="1">
         <v>8.0</v>
@@ -4092,7 +4139,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4115,25 +4162,25 @@
       <c r="O67" s="1">
         <v>10.0</v>
       </c>
-      <c r="P67" s="3">
+      <c r="P67" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q67" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R67" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="S67" s="3">
-        <v>18.0</v>
+      <c r="Q67" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S67" s="1">
+        <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68">
       <c r="E68" s="1" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="F68" s="1">
         <v>0.0</v>
@@ -4142,7 +4189,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4165,20 +4212,523 @@
       <c r="O68" s="1">
         <v>10.0</v>
       </c>
-      <c r="P68" s="3">
+      <c r="P68" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q68" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="R68" s="3">
+      <c r="Q68" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="J69" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="K69" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L69" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M69" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N69" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O69" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P69" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R69" s="2">
         <v>30.0</v>
       </c>
-      <c r="S68" s="3">
+      <c r="S69" s="2">
         <v>18.0</v>
       </c>
-      <c r="T68" s="1" t="s">
-        <v>41</v>
+      <c r="T69" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="E70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F70" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I70" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J70" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="K70" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="M70" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N70" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="O70" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P70" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R70" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S70" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T70" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="E71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F71" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="J71" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="K71" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L71" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M71" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N71" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O71" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P71" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R71" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S71" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T71" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="E72" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I72" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="J72" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K72" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L72" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M72" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N72" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O72" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P72" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R72" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S72" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="E73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F73" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I73" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="J73" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="K73" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L73" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M73" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N73" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O73" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P73" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R73" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S73" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T73" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="E74" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="J74" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="K74" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L74" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M74" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N74" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O74" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P74" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R74" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S74" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="E75" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="J75" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="K75" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L75" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M75" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N75" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O75" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P75" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R75" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S75" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T75" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="E76" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="J76" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="K76" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L76" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M76" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N76" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O76" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P76" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R76" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S76" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T76" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="E77" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F77" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I77" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="J77" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="K77" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L77" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="M77" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N77" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O77" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P77" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R77" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S77" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T77" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="E78" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="J78" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="K78" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="L78" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="O78" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="P78" s="2">
+        <v>24.0</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="R78" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="S78" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="T78" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -4203,26 +4753,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5244,186 +5794,186 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>46</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>36</v>
+      <c r="B8" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>15</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,30 +15,60 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="96">
   <si>
+    <t>Setting</t>
+  </si>
+  <si>
     <t>Project</t>
   </si>
   <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>Type</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
     <t>BUA</t>
   </si>
   <si>
+    <t>Alahly Sabbour</t>
+  </si>
+  <si>
     <t>Phase</t>
   </si>
   <si>
+    <t>Currency</t>
+  </si>
+  <si>
     <t>Plan</t>
   </si>
   <si>
+    <t>EGP</t>
+  </si>
+  <si>
     <t>Years</t>
   </si>
   <si>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
+  </si>
+  <si>
     <t>Discount %</t>
   </si>
   <si>
     <t>Down Payment Type</t>
   </si>
   <si>
+    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
+  </si>
+  <si>
     <t>Down Payment 1 %</t>
   </si>
   <si>
@@ -57,30 +87,102 @@
     <t>First Installment Due (months)</t>
   </si>
   <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
     <t>Maintenance %</t>
   </si>
   <si>
     <t>Delivery (months)</t>
   </si>
   <si>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+  </si>
+  <si>
     <t>Maintenance Basis</t>
   </si>
   <si>
     <t>YOUD</t>
   </si>
   <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Meaning / المعنى</t>
+  </si>
+  <si>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+  </si>
+  <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+  </si>
+  <si>
     <t>Original Price</t>
   </si>
   <si>
+    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
+  </si>
+  <si>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
+  </si>
+  <si>
+    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
+  </si>
+  <si>
+    <t>Second down payment, 0 if none / المقدم الثاني</t>
+  </si>
+  <si>
+    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
+  </si>
+  <si>
+    <t>Number of equal installments / عدد الأقساط</t>
+  </si>
+  <si>
+    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
+  </si>
+  <si>
+    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
+  </si>
+  <si>
+    <t>Admin Fee %</t>
+  </si>
+  <si>
+    <t>% of system price, paid upfront / رسوم إدارية</t>
+  </si>
+  <si>
+    <t>Operations Fee %</t>
+  </si>
+  <si>
+    <t>% of system price, paid upfront / رسوم تشغيل</t>
+  </si>
+  <si>
+    <t>% of system price, due at delivery / وديعة الصيانة</t>
+  </si>
+  <si>
+    <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
+  </si>
+  <si>
+    <t>After editing: save the file, then refresh the page in the browser.</t>
+  </si>
+  <si>
+    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
+  </si>
+  <si>
     <t>Selling price</t>
   </si>
   <si>
@@ -115,108 +217,6 @@
   </si>
   <si>
     <t>YOUD EL BAHR</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>Alahly Sabbour</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>How to fill the Projects sheet</t>
-  </si>
-  <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
-    <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
-  </si>
-  <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
-  </si>
-  <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
-  </si>
-  <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Meaning / المعنى</t>
-  </si>
-  <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
-  </si>
-  <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
-  </si>
-  <si>
-    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
-  </si>
-  <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
-  </si>
-  <si>
-    <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
-  </si>
-  <si>
-    <t>Second down payment, 0 if none / المقدم الثاني</t>
-  </si>
-  <si>
-    <t>When DP2 is due, months after contract / استحقاق المقدم الثاني بعد كام شهر</t>
-  </si>
-  <si>
-    <t>Number of equal installments / عدد الأقساط</t>
-  </si>
-  <si>
-    <t>3 = quarterly, 1 = monthly / الفترة بين الأقساط بالشهور</t>
-  </si>
-  <si>
-    <t>When installment 1 is due, months after contract / استحقاق أول قسط</t>
-  </si>
-  <si>
-    <t>Admin Fee %</t>
-  </si>
-  <si>
-    <t>% of system price, paid upfront / رسوم إدارية</t>
-  </si>
-  <si>
-    <t>Operations Fee %</t>
-  </si>
-  <si>
-    <t>% of system price, paid upfront / رسوم تشغيل</t>
-  </si>
-  <si>
-    <t>% of system price, due at delivery / وديعة الصيانة</t>
-  </si>
-  <si>
-    <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
-  </si>
-  <si>
-    <t>After editing: save the file, then refresh the page in the browser.</t>
-  </si>
-  <si>
-    <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
   </si>
   <si>
     <t>RTM</t>
@@ -600,75 +600,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -715,15 +715,15 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="s">
-        <v>19</v>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F3" s="1">
         <v>8.0</v>
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -770,15 +770,15 @@
         <v>6.0</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="s">
-        <v>19</v>
+      <c r="B4" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F4" s="1">
         <v>8.0</v>
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -825,15 +825,15 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="s">
-        <v>19</v>
+      <c r="B5" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F5" s="1">
         <v>8.0</v>
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -865,10 +865,10 @@
       <c r="O5" s="1">
         <v>10.0</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="3">
         <v>18.0</v>
       </c>
       <c r="R5" s="1">
@@ -879,15 +879,15 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="s">
-        <v>19</v>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1">
         <v>8.0</v>
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -919,10 +919,10 @@
       <c r="O6" s="1">
         <v>10.0</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="3">
         <v>18.0</v>
       </c>
       <c r="R6" s="1">
@@ -933,15 +933,15 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="s">
-        <v>19</v>
+      <c r="B7" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1">
         <v>8.0</v>
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -973,10 +973,10 @@
       <c r="O7" s="1">
         <v>10.0</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="3">
         <v>18.0</v>
       </c>
       <c r="R7" s="1">
@@ -987,15 +987,15 @@
         <v>6.0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="s">
-        <v>19</v>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F8" s="1">
         <v>8.0</v>
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1027,10 +1027,10 @@
       <c r="O8" s="1">
         <v>10.0</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="3">
         <v>18.0</v>
       </c>
       <c r="R8" s="1">
@@ -1041,15 +1041,15 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="s">
-        <v>19</v>
+      <c r="B9" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F9" s="1">
         <v>8.0</v>
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1081,10 +1081,10 @@
       <c r="O9" s="1">
         <v>10.0</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="3">
         <v>18.0</v>
       </c>
       <c r="R9" s="1">
@@ -1095,15 +1095,15 @@
         <v>6.0</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="s">
-        <v>19</v>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F10" s="1">
         <v>8.0</v>
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1135,10 +1135,10 @@
       <c r="O10" s="1">
         <v>10.0</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="3">
         <v>36.0</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="3">
         <v>18.0</v>
       </c>
       <c r="R10" s="1">
@@ -1149,18 +1149,18 @@
         <v>6.0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="s">
-        <v>19</v>
+      <c r="B11" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F11" s="1">
         <v>0.0</v>
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1195,28 +1195,28 @@
       <c r="P11" s="1">
         <v>24.0</v>
       </c>
-      <c r="Q11" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R11" s="2">
+      <c r="Q11" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R11" s="3">
         <v>18.0</v>
       </c>
       <c r="S11" s="1">
         <v>6.0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="3">
         <v>4.0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F12" s="1">
         <v>0.0</v>
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1262,15 +1262,15 @@
         <v>6.0</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="s">
-        <v>33</v>
+      <c r="B13" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1279,7 +1279,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1317,15 +1317,15 @@
         <v>6.0</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="s">
-        <v>33</v>
+      <c r="B14" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F14" s="1">
         <v>8.0</v>
@@ -1334,7 +1334,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1372,15 +1372,15 @@
         <v>6.0</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="s">
-        <v>33</v>
+      <c r="B15" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F15" s="1">
         <v>8.0</v>
@@ -1389,7 +1389,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1427,15 +1427,15 @@
         <v>6.0</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="s">
-        <v>33</v>
+      <c r="B16" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F16" s="1">
         <v>8.0</v>
@@ -1444,7 +1444,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1482,15 +1482,15 @@
         <v>6.0</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="s">
-        <v>33</v>
+      <c r="B17" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F17" s="1">
         <v>8.0</v>
@@ -1499,7 +1499,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1537,15 +1537,15 @@
         <v>6.0</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="s">
-        <v>33</v>
+      <c r="B18" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F18" s="1">
         <v>8.0</v>
@@ -1554,7 +1554,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1592,15 +1592,15 @@
         <v>6.0</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="s">
-        <v>33</v>
+      <c r="B19" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F19" s="1">
         <v>8.0</v>
@@ -1609,7 +1609,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1647,15 +1647,15 @@
         <v>6.0</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="s">
-        <v>33</v>
+      <c r="B20" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F20" s="1">
         <v>8.0</v>
@@ -1664,7 +1664,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1702,15 +1702,15 @@
         <v>6.0</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="s">
-        <v>33</v>
+      <c r="B21" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F21" s="1">
         <v>8.0</v>
@@ -1719,7 +1719,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1757,15 +1757,15 @@
         <v>6.0</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="s">
-        <v>33</v>
+      <c r="B22" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F22" s="1">
         <v>0.0</v>
@@ -1774,7 +1774,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1812,7 +1812,7 @@
         <v>6.0</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -1829,7 +1829,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -1865,14 +1865,14 @@
         <v>3.0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>70</v>
       </c>
       <c r="F24" s="1">
@@ -1882,24 +1882,24 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" s="2">
+        <v>39</v>
+      </c>
+      <c r="I24" s="3">
         <v>15.0</v>
       </c>
-      <c r="J24" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="2">
+      <c r="J24" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="3">
         <v>12.0</v>
       </c>
       <c r="M24" s="1">
         <v>3.0</v>
       </c>
-      <c r="N24" s="2">
+      <c r="N24" s="3">
         <v>3.0</v>
       </c>
       <c r="O24" s="1">
@@ -1918,14 +1918,14 @@
         <v>3.0</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>71</v>
       </c>
       <c r="F25" s="1">
@@ -1935,24 +1935,24 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="2">
+        <v>39</v>
+      </c>
+      <c r="I25" s="3">
         <v>20.0</v>
       </c>
-      <c r="J25" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="2">
+      <c r="J25" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="3">
         <v>16.0</v>
       </c>
       <c r="M25" s="1">
         <v>3.0</v>
       </c>
-      <c r="N25" s="2">
+      <c r="N25" s="3">
         <v>3.0</v>
       </c>
       <c r="O25" s="1">
@@ -1971,14 +1971,14 @@
         <v>3.0</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F26" s="1">
@@ -1988,24 +1988,24 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="2">
+        <v>39</v>
+      </c>
+      <c r="I26" s="3">
         <v>25.0</v>
       </c>
-      <c r="J26" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="2">
+      <c r="J26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="3">
         <v>20.0</v>
       </c>
       <c r="M26" s="1">
         <v>3.0</v>
       </c>
-      <c r="N26" s="2">
+      <c r="N26" s="3">
         <v>3.0</v>
       </c>
       <c r="O26" s="1">
@@ -2024,14 +2024,14 @@
         <v>3.0</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F27" s="1">
@@ -2041,24 +2041,24 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="2">
+        <v>39</v>
+      </c>
+      <c r="I27" s="3">
         <v>30.0</v>
       </c>
-      <c r="J27" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="2">
+      <c r="J27" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="3">
         <v>24.0</v>
       </c>
       <c r="M27" s="1">
         <v>3.0</v>
       </c>
-      <c r="N27" s="2">
+      <c r="N27" s="3">
         <v>3.0</v>
       </c>
       <c r="O27" s="1">
@@ -2077,14 +2077,14 @@
         <v>3.0</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F28" s="1">
@@ -2094,24 +2094,24 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="2">
+        <v>39</v>
+      </c>
+      <c r="I28" s="3">
         <v>35.0</v>
       </c>
-      <c r="J28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="2">
+      <c r="J28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="3">
         <v>28.0</v>
       </c>
       <c r="M28" s="1">
         <v>3.0</v>
       </c>
-      <c r="N28" s="2">
+      <c r="N28" s="3">
         <v>3.0</v>
       </c>
       <c r="O28" s="1">
@@ -2130,14 +2130,14 @@
         <v>3.0</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>75</v>
       </c>
       <c r="F29" s="1">
@@ -2147,24 +2147,24 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="2">
+        <v>39</v>
+      </c>
+      <c r="I29" s="3">
         <v>40.0</v>
       </c>
-      <c r="J29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="2">
+      <c r="J29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="3">
         <v>32.0</v>
       </c>
       <c r="M29" s="1">
         <v>3.0</v>
       </c>
-      <c r="N29" s="2">
+      <c r="N29" s="3">
         <v>3.0</v>
       </c>
       <c r="O29" s="1">
@@ -2183,7 +2183,7 @@
         <v>3.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
@@ -2200,7 +2200,7 @@
         <v>15.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I30" s="1">
         <v>100.0</v>
@@ -2236,432 +2236,432 @@
         <v>3.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>4.0</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="J31" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="2">
+        <v>39</v>
+      </c>
+      <c r="I31" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="3">
         <v>0.0</v>
       </c>
       <c r="L31" s="1">
         <f>4*4</f>
         <v>16</v>
       </c>
-      <c r="M31" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N31" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="O31" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P31" s="2">
+      <c r="M31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N31" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P31" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q31" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R31" s="2">
+      <c r="Q31" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R31" s="3">
         <v>15.0</v>
       </c>
-      <c r="S31" s="2">
+      <c r="S31" s="3">
         <v>3.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>5.0</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="3">
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I32" s="2">
+        <v>39</v>
+      </c>
+      <c r="I32" s="3">
         <v>7.5</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="3">
         <v>7.5</v>
       </c>
-      <c r="K32" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L32" s="2">
+      <c r="K32" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L32" s="3">
         <v>19.0</v>
       </c>
-      <c r="M32" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N32" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O32" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P32" s="2">
+      <c r="M32" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P32" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q32" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R32" s="2">
+      <c r="Q32" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R32" s="3">
         <v>15.0</v>
       </c>
-      <c r="S32" s="2">
+      <c r="S32" s="3">
         <v>3.0</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F33" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="G33" s="2">
+      <c r="F33" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="G33" s="3">
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I33" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="J33" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="K33" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L33" s="2">
+        <v>39</v>
+      </c>
+      <c r="I33" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L33" s="3">
         <v>23.0</v>
       </c>
-      <c r="M33" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N33" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O33" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P33" s="2">
+      <c r="M33" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N33" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O33" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P33" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q33" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R33" s="2">
+      <c r="Q33" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R33" s="3">
         <v>15.0</v>
       </c>
-      <c r="S33" s="2">
+      <c r="S33" s="3">
         <v>3.0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>7.0</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="3">
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I34" s="2">
+        <v>39</v>
+      </c>
+      <c r="I34" s="3">
         <v>12.5</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="3">
         <v>12.5</v>
       </c>
-      <c r="K34" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L34" s="2">
+      <c r="K34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L34" s="3">
         <v>27.0</v>
       </c>
-      <c r="M34" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N34" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O34" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P34" s="2">
+      <c r="M34" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N34" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P34" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q34" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R34" s="2">
+      <c r="Q34" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R34" s="3">
         <v>15.0</v>
       </c>
-      <c r="S34" s="2">
+      <c r="S34" s="3">
         <v>3.0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>8.0</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="3">
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I35" s="2">
+        <v>39</v>
+      </c>
+      <c r="I35" s="3">
         <v>15.0</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="3">
         <v>15.0</v>
       </c>
-      <c r="K35" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L35" s="2">
+      <c r="K35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L35" s="3">
         <v>31.0</v>
       </c>
-      <c r="M35" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N35" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O35" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P35" s="2">
+      <c r="M35" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N35" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O35" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P35" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q35" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R35" s="2">
+      <c r="Q35" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R35" s="3">
         <v>15.0</v>
       </c>
-      <c r="S35" s="2">
+      <c r="S35" s="3">
         <v>3.0</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>9.0</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="3">
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="2">
+        <v>39</v>
+      </c>
+      <c r="I36" s="3">
         <v>17.5</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="3">
         <v>17.5</v>
       </c>
-      <c r="K36" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L36" s="2">
+      <c r="K36" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L36" s="3">
         <v>35.0</v>
       </c>
-      <c r="M36" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N36" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O36" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P36" s="2">
+      <c r="M36" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N36" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O36" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P36" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q36" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R36" s="2">
+      <c r="Q36" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R36" s="3">
         <v>15.0</v>
       </c>
-      <c r="S36" s="2">
+      <c r="S36" s="3">
         <v>3.0</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F37" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="G37" s="2">
+      <c r="F37" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G37" s="3">
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I37" s="2">
+        <v>39</v>
+      </c>
+      <c r="I37" s="3">
         <v>20.0</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="3">
         <v>20.0</v>
       </c>
-      <c r="K37" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="L37" s="2">
+      <c r="K37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="L37" s="3">
         <v>39.0</v>
       </c>
-      <c r="M37" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="N37" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="O37" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P37" s="2">
+      <c r="M37" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="N37" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="O37" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P37" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q37" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R37" s="2">
+      <c r="Q37" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R37" s="3">
         <v>15.0</v>
       </c>
-      <c r="S37" s="2">
+      <c r="S37" s="3">
         <v>3.0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G38" s="2">
+      <c r="F38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G38" s="3">
         <v>15.0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="2">
+        <v>56</v>
+      </c>
+      <c r="I38" s="3">
         <v>100.0</v>
       </c>
-      <c r="J38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="K38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P38" s="2">
+      <c r="J38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="L38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="P38" s="3">
         <v>12.0</v>
       </c>
-      <c r="Q38" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R38" s="2">
+      <c r="Q38" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R38" s="3">
         <v>15.0</v>
       </c>
-      <c r="S38" s="2">
+      <c r="S38" s="3">
         <v>3.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39">
@@ -2681,7 +2681,7 @@
         <v>25.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I39" s="1">
         <v>100.0</v>
@@ -2717,7 +2717,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -2734,7 +2734,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2770,7 +2770,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -2787,7 +2787,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2798,8 +2798,8 @@
       <c r="K41" s="1">
         <v>3.0</v>
       </c>
-      <c r="L41" s="1">
-        <v>31.0</v>
+      <c r="L41" s="3">
+        <v>27.0</v>
       </c>
       <c r="M41" s="1">
         <v>3.0</v>
@@ -2823,7 +2823,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
@@ -2840,7 +2840,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -2851,8 +2851,8 @@
       <c r="K42" s="1">
         <v>3.0</v>
       </c>
-      <c r="L42" s="1">
-        <v>31.0</v>
+      <c r="L42" s="3">
+        <v>23.0</v>
       </c>
       <c r="M42" s="1">
         <v>3.0</v>
@@ -2876,7 +2876,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
@@ -2893,7 +2893,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -2904,8 +2904,8 @@
       <c r="K43" s="1">
         <v>3.0</v>
       </c>
-      <c r="L43" s="1">
-        <v>31.0</v>
+      <c r="L43" s="3">
+        <v>19.0</v>
       </c>
       <c r="M43" s="1">
         <v>3.0</v>
@@ -2929,7 +2929,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
@@ -2949,7 +2949,7 @@
         <v>25.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I44" s="1">
         <v>100.0</v>
@@ -2985,7 +2985,7 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45">
@@ -3005,7 +3005,7 @@
         <v>0.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I45" s="1">
         <v>5.0</v>
@@ -3041,7 +3041,7 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
@@ -3061,7 +3061,7 @@
         <v>3.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I46" s="1">
         <v>5.0</v>
@@ -3072,8 +3072,8 @@
       <c r="K46" s="1">
         <v>3.0</v>
       </c>
-      <c r="L46" s="1">
-        <v>31.0</v>
+      <c r="L46" s="3">
+        <v>27.0</v>
       </c>
       <c r="M46" s="1">
         <v>3.0</v>
@@ -3097,7 +3097,7 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -3117,7 +3117,7 @@
         <v>6.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I47" s="1">
         <v>5.0</v>
@@ -3128,8 +3128,8 @@
       <c r="K47" s="1">
         <v>3.0</v>
       </c>
-      <c r="L47" s="1">
-        <v>31.0</v>
+      <c r="L47" s="3">
+        <v>23.0</v>
       </c>
       <c r="M47" s="1">
         <v>3.0</v>
@@ -3153,7 +3153,7 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
@@ -3173,7 +3173,7 @@
         <v>9.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="I48" s="1">
         <v>5.0</v>
@@ -3184,8 +3184,8 @@
       <c r="K48" s="1">
         <v>3.0</v>
       </c>
-      <c r="L48" s="1">
-        <v>31.0</v>
+      <c r="L48" s="3">
+        <v>19.0</v>
       </c>
       <c r="M48" s="1">
         <v>3.0</v>
@@ -3209,7 +3209,7 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49">
@@ -3217,7 +3217,7 @@
         <v>93</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3226,7 +3226,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3263,12 +3263,12 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
       <c r="E50" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F50" s="1">
         <v>8.0</v>
@@ -3277,7 +3277,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3314,12 +3314,12 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51">
       <c r="E51" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F51" s="1">
         <v>8.0</v>
@@ -3328,7 +3328,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3365,12 +3365,12 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52">
       <c r="E52" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F52" s="1">
         <v>8.0</v>
@@ -3379,7 +3379,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3416,12 +3416,12 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53">
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F53" s="1">
         <v>8.0</v>
@@ -3430,7 +3430,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3467,12 +3467,12 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54">
       <c r="E54" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F54" s="1">
         <v>8.0</v>
@@ -3481,7 +3481,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3518,12 +3518,12 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55">
       <c r="E55" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F55" s="1">
         <v>8.0</v>
@@ -3532,7 +3532,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3569,12 +3569,12 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="56">
       <c r="E56" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F56" s="1">
         <v>8.0</v>
@@ -3583,7 +3583,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3620,12 +3620,12 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57">
       <c r="E57" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F57" s="1">
         <v>8.0</v>
@@ -3634,7 +3634,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3671,12 +3671,12 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58">
       <c r="E58" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F58" s="1">
         <v>0.0</v>
@@ -3685,7 +3685,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3722,7 +3722,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
@@ -3730,7 +3730,7 @@
         <v>94</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3739,7 +3739,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3775,12 +3775,12 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F60" s="1">
         <v>8.0</v>
@@ -3789,7 +3789,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3825,12 +3825,12 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
       <c r="E61" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F61" s="1">
         <v>8.0</v>
@@ -3839,7 +3839,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3875,12 +3875,12 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62">
       <c r="E62" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F62" s="1">
         <v>8.0</v>
@@ -3889,7 +3889,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3925,12 +3925,12 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63">
       <c r="E63" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F63" s="1">
         <v>8.0</v>
@@ -3939,7 +3939,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3975,12 +3975,12 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64">
       <c r="E64" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F64" s="1">
         <v>8.0</v>
@@ -3989,7 +3989,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4025,12 +4025,12 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65">
       <c r="E65" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F65" s="1">
         <v>8.0</v>
@@ -4039,7 +4039,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4075,12 +4075,12 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66">
       <c r="E66" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F66" s="1">
         <v>8.0</v>
@@ -4089,7 +4089,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4125,12 +4125,12 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67">
       <c r="E67" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F67" s="1">
         <v>8.0</v>
@@ -4139,7 +4139,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4175,12 +4175,12 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68">
       <c r="E68" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F68" s="1">
         <v>0.0</v>
@@ -4189,7 +4189,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4225,15 +4225,15 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4242,7 +4242,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4265,25 +4265,25 @@
       <c r="O69" s="1">
         <v>10.0</v>
       </c>
-      <c r="P69" s="2">
+      <c r="P69" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q69" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R69" s="2">
+      <c r="Q69" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R69" s="3">
         <v>30.0</v>
       </c>
-      <c r="S69" s="2">
+      <c r="S69" s="3">
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70">
       <c r="E70" s="1" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F70" s="1">
         <v>8.0</v>
@@ -4292,7 +4292,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4315,25 +4315,25 @@
       <c r="O70" s="1">
         <v>10.0</v>
       </c>
-      <c r="P70" s="2">
+      <c r="P70" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q70" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R70" s="2">
+      <c r="Q70" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R70" s="3">
         <v>30.0</v>
       </c>
-      <c r="S70" s="2">
+      <c r="S70" s="3">
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71">
       <c r="E71" s="1" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F71" s="1">
         <v>8.0</v>
@@ -4342,7 +4342,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4365,25 +4365,25 @@
       <c r="O71" s="1">
         <v>10.0</v>
       </c>
-      <c r="P71" s="2">
+      <c r="P71" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q71" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R71" s="2">
+      <c r="Q71" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R71" s="3">
         <v>30.0</v>
       </c>
-      <c r="S71" s="2">
+      <c r="S71" s="3">
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72">
       <c r="E72" s="1" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="F72" s="1">
         <v>8.0</v>
@@ -4392,7 +4392,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4415,25 +4415,25 @@
       <c r="O72" s="1">
         <v>10.0</v>
       </c>
-      <c r="P72" s="2">
+      <c r="P72" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q72" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R72" s="2">
+      <c r="Q72" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R72" s="3">
         <v>30.0</v>
       </c>
-      <c r="S72" s="2">
+      <c r="S72" s="3">
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="73">
       <c r="E73" s="1" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F73" s="1">
         <v>8.0</v>
@@ -4442,7 +4442,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4465,25 +4465,25 @@
       <c r="O73" s="1">
         <v>10.0</v>
       </c>
-      <c r="P73" s="2">
+      <c r="P73" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q73" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R73" s="2">
+      <c r="Q73" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R73" s="3">
         <v>30.0</v>
       </c>
-      <c r="S73" s="2">
+      <c r="S73" s="3">
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74">
       <c r="E74" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="F74" s="1">
         <v>8.0</v>
@@ -4492,7 +4492,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4515,25 +4515,25 @@
       <c r="O74" s="1">
         <v>10.0</v>
       </c>
-      <c r="P74" s="2">
+      <c r="P74" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q74" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R74" s="2">
+      <c r="Q74" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R74" s="3">
         <v>30.0</v>
       </c>
-      <c r="S74" s="2">
+      <c r="S74" s="3">
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75">
       <c r="E75" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="F75" s="1">
         <v>8.0</v>
@@ -4542,7 +4542,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4565,25 +4565,25 @@
       <c r="O75" s="1">
         <v>10.0</v>
       </c>
-      <c r="P75" s="2">
+      <c r="P75" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q75" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R75" s="2">
+      <c r="Q75" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R75" s="3">
         <v>30.0</v>
       </c>
-      <c r="S75" s="2">
+      <c r="S75" s="3">
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76">
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F76" s="1">
         <v>8.0</v>
@@ -4592,7 +4592,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4615,25 +4615,25 @@
       <c r="O76" s="1">
         <v>10.0</v>
       </c>
-      <c r="P76" s="2">
+      <c r="P76" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q76" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R76" s="2">
+      <c r="Q76" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R76" s="3">
         <v>30.0</v>
       </c>
-      <c r="S76" s="2">
+      <c r="S76" s="3">
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77">
       <c r="E77" s="1" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F77" s="1">
         <v>8.0</v>
@@ -4642,7 +4642,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4665,25 +4665,25 @@
       <c r="O77" s="1">
         <v>10.0</v>
       </c>
-      <c r="P77" s="2">
+      <c r="P77" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q77" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R77" s="2">
+      <c r="Q77" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R77" s="3">
         <v>30.0</v>
       </c>
-      <c r="S77" s="2">
+      <c r="S77" s="3">
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78">
       <c r="E78" s="1" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F78" s="1">
         <v>0.0</v>
@@ -4692,7 +4692,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -4715,20 +4715,20 @@
       <c r="O78" s="1">
         <v>10.0</v>
       </c>
-      <c r="P78" s="2">
+      <c r="P78" s="3">
         <v>24.0</v>
       </c>
-      <c r="Q78" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="R78" s="2">
+      <c r="Q78" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="R78" s="3">
         <v>30.0</v>
       </c>
-      <c r="S78" s="2">
+      <c r="S78" s="3">
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -4753,26 +4753,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5794,186 +5794,186 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>45</v>
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>50</v>
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>53</v>
+        <v>15</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" ht="15.0" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="15.0" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>56</v>
+        <v>20</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>58</v>
+        <v>22</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" ht="15.0" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>65</v>
+        <v>26</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>67</v>
+        <v>54</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -21,10 +21,16 @@
     <t>Project</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
     <t>How to fill the Projects sheet</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Alahly Sabbour</t>
   </si>
   <si>
     <t>Type</t>
@@ -33,33 +39,27 @@
     <t/>
   </si>
   <si>
-    <t>Company Name</t>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>EGP</t>
   </si>
   <si>
     <t>BUA</t>
   </si>
   <si>
-    <t>Alahly Sabbour</t>
-  </si>
-  <si>
     <t>Phase</t>
   </si>
   <si>
-    <t>Currency</t>
-  </si>
-  <si>
     <t>Plan</t>
   </si>
   <si>
-    <t>EGP</t>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
   </si>
   <si>
     <t>Years</t>
   </si>
   <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
     <t>Discount %</t>
   </si>
   <si>
@@ -78,16 +78,25 @@
     <t>DP2 Due (months)</t>
   </si>
   <si>
+    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+  </si>
+  <si>
     <t>Installments Count</t>
   </si>
   <si>
+    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
+  </si>
+  <si>
     <t>Installment Every (months)</t>
   </si>
   <si>
+    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+  </si>
+  <si>
     <t>First Installment Due (months)</t>
   </si>
   <si>
-    <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
+    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
     <t>Maintenance %</t>
@@ -96,19 +105,19 @@
     <t>Delivery (months)</t>
   </si>
   <si>
-    <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
-  </si>
-  <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
-    <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Meaning / المعنى</t>
   </si>
   <si>
     <t>Ending Installment Maintenance Due (months)</t>
   </si>
   <si>
-    <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
+    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
   </si>
   <si>
     <t>Maintenance Basis</t>
@@ -117,30 +126,21 @@
     <t>YOUD</t>
   </si>
   <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Meaning / المعنى</t>
-  </si>
-  <si>
-    <t>Project name. Leave blank to repeat the project above. / اسم المشروع — سيبها فاضية لتكرار اللي فوق</t>
+    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+  </si>
+  <si>
+    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
   </si>
   <si>
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
-    <t>Plan label shown in the dropdown, e.g. "8 Years" or "Cash" / اسم نظام السداد</t>
+    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
     <t>Original Price</t>
   </si>
   <si>
-    <t>Plan length in years, 0 for cash (informational) / مدة النظام بالسنين</t>
-  </si>
-  <si>
-    <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
-  </si>
-  <si>
     <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
   </si>
   <si>
@@ -252,22 +252,22 @@
     <t>10% DP over 4 years</t>
   </si>
   <si>
-    <t>7.5% DP &amp; 7.5% After 3 months over 5 years</t>
-  </si>
-  <si>
-    <t>10% DP &amp; 10% After 3 months over 6 years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5% DP &amp; 12.5% After 3 months over 7 years </t>
-  </si>
-  <si>
-    <t xml:space="preserve">15% DP &amp; 15% After 3 months over 8 years </t>
-  </si>
-  <si>
-    <t>17.5% DP &amp; 17.5% After 3 months over 9 years</t>
-  </si>
-  <si>
-    <t>20% DP &amp; 20% After 3 months over 10 years</t>
+    <t>15% DP over 5 years</t>
+  </si>
+  <si>
+    <t>20% DP over 6 years</t>
+  </si>
+  <si>
+    <t>25% DP over 7 years</t>
+  </si>
+  <si>
+    <t>30% DP over 8 years</t>
+  </si>
+  <si>
+    <t>35% DP over 9 years</t>
+  </si>
+  <si>
+    <t>40% DP over 10 years</t>
   </si>
   <si>
     <t>The Mornings_Everyday</t>
@@ -603,19 +603,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -633,42 +633,42 @@
         <v>20</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F2" s="1">
         <v>8.0</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="3">
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>57</v>
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="4">
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>58</v>
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -830,7 +830,7 @@
     </row>
     <row r="5">
       <c r="B5" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>59</v>
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="6">
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>60</v>
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="7">
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>61</v>
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -992,7 +992,7 @@
     </row>
     <row r="8">
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>62</v>
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="9">
       <c r="B9" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>63</v>
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1100,7 +1100,7 @@
     </row>
     <row r="10">
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>64</v>
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="11">
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>65</v>
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="12">
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D12" s="3">
         <v>4.0</v>
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1270,7 +1270,7 @@
         <v>67</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1">
         <v>8.0</v>
@@ -1279,7 +1279,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1334,7 +1334,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1389,7 +1389,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1444,7 +1444,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1499,7 +1499,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1554,7 +1554,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1609,7 +1609,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1664,7 +1664,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1719,7 +1719,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1774,7 +1774,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1829,7 +1829,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -1882,7 +1882,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -1935,7 +1935,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -1988,7 +1988,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2041,7 +2041,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2094,7 +2094,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2147,7 +2147,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2253,7 +2253,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2307,19 +2307,19 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I32" s="3">
-        <v>7.5</v>
+        <v>15.0</v>
       </c>
       <c r="J32" s="3">
-        <v>7.5</v>
+        <v>0.0</v>
       </c>
       <c r="K32" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L32" s="3">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="M32" s="3">
         <v>3.0</v>
@@ -2360,19 +2360,19 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I33" s="3">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="J33" s="3">
-        <v>10.0</v>
+        <v>0.0</v>
       </c>
       <c r="K33" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L33" s="3">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="M33" s="3">
         <v>3.0</v>
@@ -2413,19 +2413,19 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I34" s="3">
-        <v>12.5</v>
+        <v>25.0</v>
       </c>
       <c r="J34" s="3">
-        <v>12.5</v>
+        <v>0.0</v>
       </c>
       <c r="K34" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L34" s="3">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="M34" s="3">
         <v>3.0</v>
@@ -2466,19 +2466,19 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I35" s="3">
-        <v>15.0</v>
+        <v>30.0</v>
       </c>
       <c r="J35" s="3">
-        <v>15.0</v>
+        <v>0.0</v>
       </c>
       <c r="K35" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L35" s="3">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="M35" s="3">
         <v>3.0</v>
@@ -2519,19 +2519,19 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I36" s="3">
-        <v>17.5</v>
+        <v>35.0</v>
       </c>
       <c r="J36" s="3">
-        <v>17.5</v>
+        <v>0.0</v>
       </c>
       <c r="K36" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L36" s="3">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="M36" s="3">
         <v>3.0</v>
@@ -2572,19 +2572,19 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I37" s="3">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="J37" s="3">
-        <v>20.0</v>
+        <v>0.0</v>
       </c>
       <c r="K37" s="3">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="L37" s="3">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="M37" s="3">
         <v>3.0</v>
@@ -2717,7 +2717,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -2734,7 +2734,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2770,7 +2770,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
@@ -2787,7 +2787,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2823,7 +2823,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -2840,7 +2840,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -2876,7 +2876,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -2893,7 +2893,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -2929,7 +2929,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
@@ -3217,7 +3217,7 @@
         <v>93</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F49" s="1">
         <v>8.0</v>
@@ -3226,7 +3226,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3263,7 +3263,7 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50">
@@ -3277,7 +3277,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3314,7 +3314,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
@@ -3328,7 +3328,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3365,7 +3365,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
@@ -3379,7 +3379,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3416,7 +3416,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53">
@@ -3430,7 +3430,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3467,7 +3467,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54">
@@ -3481,7 +3481,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3518,7 +3518,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
@@ -3532,7 +3532,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3569,7 +3569,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56">
@@ -3583,7 +3583,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3620,7 +3620,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57">
@@ -3634,7 +3634,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3671,7 +3671,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
@@ -3685,7 +3685,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3722,7 +3722,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59">
@@ -3730,7 +3730,7 @@
         <v>94</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F59" s="1">
         <v>8.0</v>
@@ -3739,7 +3739,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3775,7 +3775,7 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60">
@@ -3789,7 +3789,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3825,7 +3825,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61">
@@ -3839,7 +3839,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3875,7 +3875,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
@@ -3889,7 +3889,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3925,7 +3925,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63">
@@ -3939,7 +3939,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3975,7 +3975,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
@@ -3989,7 +3989,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4025,7 +4025,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65">
@@ -4039,7 +4039,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4075,7 +4075,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
@@ -4089,7 +4089,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4125,7 +4125,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -4139,7 +4139,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4175,7 +4175,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68">
@@ -4189,7 +4189,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4225,7 +4225,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69">
@@ -4233,7 +4233,7 @@
         <v>95</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F69" s="1">
         <v>8.0</v>
@@ -4242,7 +4242,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4278,7 +4278,7 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
@@ -4292,7 +4292,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4328,7 +4328,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71">
@@ -4342,7 +4342,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4378,7 +4378,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72">
@@ -4392,7 +4392,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4428,7 +4428,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73">
@@ -4442,7 +4442,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4478,7 +4478,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
@@ -4492,7 +4492,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4528,7 +4528,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75">
@@ -4542,7 +4542,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4578,7 +4578,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76">
@@ -4592,7 +4592,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4628,7 +4628,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77">
@@ -4642,7 +4642,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4678,7 +4678,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78">
@@ -4692,7 +4692,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -4728,7 +4728,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -4756,23 +4756,23 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5794,23 +5794,23 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>17</v>
@@ -5818,34 +5818,34 @@
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" ht="15.0" customHeight="1">
@@ -5853,23 +5853,23 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" ht="15.0" customHeight="1">
@@ -5877,7 +5877,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
@@ -5906,7 +5906,7 @@
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>45</v>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>47</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>52</v>
@@ -5954,7 +5954,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>53</v>
@@ -5962,10 +5962,10 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">

--- a/public/projects.xlsx
+++ b/public/projects.xlsx
@@ -15,96 +15,96 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="96">
   <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>How to fill the Projects sheet</t>
+  </si>
+  <si>
     <t>Setting</t>
   </si>
   <si>
-    <t>Project</t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Value</t>
   </si>
   <si>
-    <t>How to fill the Projects sheet</t>
+    <t>BUA</t>
   </si>
   <si>
     <t>Company Name</t>
   </si>
   <si>
+    <t>Phase</t>
+  </si>
+  <si>
     <t>Alahly Sabbour</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t/>
+    <t>Plan</t>
   </si>
   <si>
     <t>Currency</t>
   </si>
   <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
+  </si>
+  <si>
     <t>EGP</t>
   </si>
   <si>
-    <t>BUA</t>
-  </si>
-  <si>
-    <t>Phase</t>
-  </si>
-  <si>
-    <t>Plan</t>
-  </si>
-  <si>
-    <t>Each row is ONE payment plan. Rows with a blank Project cell belong to the project above them.</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
     <t>Discount %</t>
   </si>
   <si>
     <t>Down Payment Type</t>
   </si>
   <si>
+    <t>Down Payment 1 %</t>
+  </si>
+  <si>
     <t>كل صف = نظام سداد واحد. لو خلية المشروع فاضية، الصف بيتبع المشروع اللي فوقه.</t>
   </si>
   <si>
-    <t>Down Payment 1 %</t>
-  </si>
-  <si>
     <t>Down Payment 2 %</t>
   </si>
   <si>
     <t>DP2 Due (months)</t>
   </si>
   <si>
+    <t>Installments Count</t>
+  </si>
+  <si>
     <t>All % columns are plain numbers in percent units: 10 means 10%, 0.99 means 0.99%.</t>
   </si>
   <si>
-    <t>Installments Count</t>
+    <t>Installment Every (months)</t>
   </si>
   <si>
     <t>أعمدة النسب أرقام عادية: 10 يعني 10%، و 0.99 يعني 0.99%.</t>
   </si>
   <si>
-    <t>Installment Every (months)</t>
+    <t>First Installment Due (months)</t>
+  </si>
+  <si>
+    <t>Maintenance %</t>
   </si>
   <si>
     <t>Cells formatted as % in Excel (showing "10%") are also understood correctly.</t>
   </si>
   <si>
-    <t>First Installment Due (months)</t>
+    <t>Delivery (months)</t>
   </si>
   <si>
     <t>ولو نسّقت الخلية كنسبة مئوية في إكسل، هتتفهم صح برضه.</t>
   </si>
   <si>
-    <t>Maintenance %</t>
-  </si>
-  <si>
-    <t>Delivery (months)</t>
-  </si>
-  <si>
     <t>First Installment Maintenance Due (months)</t>
   </si>
   <si>
@@ -135,12 +135,12 @@
     <t>5% DP &amp; 5% After 3 Months &amp; 8 Years</t>
   </si>
   <si>
+    <t>Original Price</t>
+  </si>
+  <si>
     <t>Discount off the system price; negative = premium / نسبة الخصم من سعر النظام</t>
   </si>
   <si>
-    <t>Original Price</t>
-  </si>
-  <si>
     <t>First down payment, % of selling price, due at contract date / المقدم الأول</t>
   </si>
   <si>
@@ -174,19 +174,19 @@
     <t>% of system price, due at delivery / وديعة الصيانة</t>
   </si>
   <si>
+    <t>Selling price</t>
+  </si>
+  <si>
     <t>Months from contract to delivery / الاستلام بعد كام شهر</t>
   </si>
   <si>
+    <t>10% DP &amp; 8 Years</t>
+  </si>
+  <si>
     <t>After editing: save the file, then refresh the page in the browser.</t>
   </si>
   <si>
     <t>بعد التعديل: احفظ الملف واعمل refresh للصفحة.</t>
-  </si>
-  <si>
-    <t>Selling price</t>
-  </si>
-  <si>
-    <t>10% DP &amp; 8 Years</t>
   </si>
   <si>
     <t>7.5% DP &amp; 7.5% After 3 Months &amp; 8 Years</t>
@@ -600,22 +600,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>15</v>
@@ -624,7 +624,7 @@
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>19</v>
@@ -633,19 +633,19 @@
         <v>20</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>30</v>
@@ -654,7 +654,7 @@
         <v>33</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>35</v>
@@ -677,7 +677,7 @@
         <v>0.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1">
         <v>5.0</v>
@@ -715,7 +715,7 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F3" s="1">
         <v>8.0</v>
@@ -732,7 +732,7 @@
         <v>10.0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1">
         <v>10.0</v>
@@ -770,7 +770,7 @@
         <v>6.0</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>15.0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1">
         <v>7.5</v>
@@ -825,7 +825,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -842,7 +842,7 @@
         <v>20.0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="1">
         <v>10.0</v>
@@ -879,7 +879,7 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -896,7 +896,7 @@
         <v>25.0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I6" s="1">
         <v>12.5</v>
@@ -933,7 +933,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -950,7 +950,7 @@
         <v>30.0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I7" s="1">
         <v>15.0</v>
@@ -987,7 +987,7 @@
         <v>6.0</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -1004,7 +1004,7 @@
         <v>35.0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I8" s="1">
         <v>17.5</v>
@@ -1041,7 +1041,7 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -1058,7 +1058,7 @@
         <v>40.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I9" s="1">
         <v>20.0</v>
@@ -1095,7 +1095,7 @@
         <v>6.0</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -1112,7 +1112,7 @@
         <v>45.0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I10" s="1">
         <v>22.5</v>
@@ -1149,7 +1149,7 @@
         <v>6.0</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -1169,7 +1169,7 @@
         <v>50.0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" s="1">
         <v>25.0</v>
@@ -1205,7 +1205,7 @@
         <v>6.0</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
@@ -1225,7 +1225,7 @@
         <v>50.0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I12" s="1">
         <v>25.0</v>
@@ -1262,7 +1262,7 @@
         <v>6.0</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         <v>0.0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I13" s="1">
         <v>5.0</v>
@@ -1317,7 +1317,7 @@
         <v>6.0</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -1325,7 +1325,7 @@
         <v>67</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F14" s="1">
         <v>8.0</v>
@@ -1334,7 +1334,7 @@
         <v>10.0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I14" s="1">
         <v>10.0</v>
@@ -1372,7 +1372,7 @@
         <v>6.0</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -1389,7 +1389,7 @@
         <v>15.0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I15" s="1">
         <v>7.5</v>
@@ -1427,7 +1427,7 @@
         <v>6.0</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
@@ -1444,7 +1444,7 @@
         <v>20.0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I16" s="1">
         <v>10.0</v>
@@ -1482,7 +1482,7 @@
         <v>6.0</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1499,7 +1499,7 @@
         <v>25.0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I17" s="1">
         <v>12.5</v>
@@ -1537,7 +1537,7 @@
         <v>6.0</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
@@ -1554,7 +1554,7 @@
         <v>30.0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I18" s="1">
         <v>15.0</v>
@@ -1592,7 +1592,7 @@
         <v>6.0</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="19">
@@ -1609,7 +1609,7 @@
         <v>35.0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I19" s="1">
         <v>17.5</v>
@@ -1647,7 +1647,7 @@
         <v>6.0</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20">
@@ -1664,7 +1664,7 @@
         <v>40.0</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I20" s="1">
         <v>20.0</v>
@@ -1702,7 +1702,7 @@
         <v>6.0</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21">
@@ -1719,7 +1719,7 @@
         <v>45.0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I21" s="1">
         <v>22.5</v>
@@ -1757,7 +1757,7 @@
         <v>6.0</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -1774,7 +1774,7 @@
         <v>50.0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I22" s="1">
         <v>25.0</v>
@@ -1812,7 +1812,7 @@
         <v>6.0</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
@@ -1829,7 +1829,7 @@
         <v>0.0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I23" s="1">
         <v>10.0</v>
@@ -1865,7 +1865,7 @@
         <v>3.0</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24">
@@ -1882,7 +1882,7 @@
         <v>0.0</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I24" s="3">
         <v>15.0</v>
@@ -1918,7 +1918,7 @@
         <v>3.0</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25">
@@ -1935,7 +1935,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I25" s="3">
         <v>20.0</v>
@@ -1971,7 +1971,7 @@
         <v>3.0</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26">
@@ -1988,7 +1988,7 @@
         <v>0.0</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I26" s="3">
         <v>25.0</v>
@@ -2024,7 +2024,7 @@
         <v>3.0</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
@@ -2041,7 +2041,7 @@
         <v>0.0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I27" s="3">
         <v>30.0</v>
@@ -2077,7 +2077,7 @@
         <v>3.0</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28">
@@ -2094,7 +2094,7 @@
         <v>0.0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I28" s="3">
         <v>35.0</v>
@@ -2130,7 +2130,7 @@
         <v>3.0</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
@@ -2147,7 +2147,7 @@
         <v>0.0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I29" s="3">
         <v>40.0</v>
@@ -2183,7 +2183,7 @@
         <v>3.0</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
@@ -2200,7 +2200,7 @@
         <v>15.0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I30" s="1">
         <v>100.0</v>
@@ -2236,7 +2236,7 @@
         <v>3.0</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
@@ -2253,7 +2253,7 @@
         <v>0.0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I31" s="3">
         <v>10.0</v>
@@ -2290,7 +2290,7 @@
         <v>3.0</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32">
@@ -2307,7 +2307,7 @@
         <v>0.0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I32" s="3">
         <v>15.0</v>
@@ -2325,7 +2325,7 @@
         <v>3.0</v>
       </c>
       <c r="N32" s="3">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="O32" s="3">
         <v>10.0</v>
@@ -2343,7 +2343,7 @@
         <v>3.0</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
@@ -2360,7 +2360,7 @@
         <v>0.0</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I33" s="3">
         <v>20.0</v>
@@ -2378,7 +2378,7 @@
         <v>3.0</v>
       </c>
       <c r="N33" s="3">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="O33" s="3">
         <v>10.0</v>
@@ -2396,7 +2396,7 @@
         <v>3.0</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
@@ -2413,7 +2413,7 @@
         <v>0.0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I34" s="3">
         <v>25.0</v>
@@ -2431,7 +2431,7 @@
         <v>3.0</v>
       </c>
       <c r="N34" s="3">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="O34" s="3">
         <v>10.0</v>
@@ -2449,7 +2449,7 @@
         <v>3.0</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35">
@@ -2466,7 +2466,7 @@
         <v>0.0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I35" s="3">
         <v>30.0</v>
@@ -2484,7 +2484,7 @@
         <v>3.0</v>
       </c>
       <c r="N35" s="3">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="O35" s="3">
         <v>10.0</v>
@@ -2502,7 +2502,7 @@
         <v>3.0</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -2519,7 +2519,7 @@
         <v>0.0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I36" s="3">
         <v>35.0</v>
@@ -2537,7 +2537,7 @@
         <v>3.0</v>
       </c>
       <c r="N36" s="3">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="O36" s="3">
         <v>10.0</v>
@@ -2555,7 +2555,7 @@
         <v>3.0</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37">
@@ -2572,7 +2572,7 @@
         <v>0.0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I37" s="3">
         <v>40.0</v>
@@ -2590,7 +2590,7 @@
         <v>3.0</v>
       </c>
       <c r="N37" s="3">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="O37" s="3">
         <v>10.0</v>
@@ -2608,7 +2608,7 @@
         <v>3.0</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38">
@@ -2625,7 +2625,7 @@
         <v>15.0</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I38" s="3">
         <v>100.0</v>
@@ -2661,7 +2661,7 @@
         <v>3.0</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
@@ -2681,7 +2681,7 @@
         <v>25.0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I39" s="1">
         <v>100.0</v>
@@ -2717,7 +2717,7 @@
         <v>6.0</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
@@ -2734,7 +2734,7 @@
         <v>0.0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I40" s="1">
         <v>5.0</v>
@@ -2770,7 +2770,7 @@
         <v>6.0</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -2787,7 +2787,7 @@
         <v>3.0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I41" s="1">
         <v>5.0</v>
@@ -2823,7 +2823,7 @@
         <v>6.0</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -2840,7 +2840,7 @@
         <v>6.0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I42" s="1">
         <v>5.0</v>
@@ -2876,7 +2876,7 @@
         <v>6.0</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -2893,7 +2893,7 @@
         <v>9.0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I43" s="1">
         <v>5.0</v>
@@ -2929,7 +2929,7 @@
         <v>6.0</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -2949,7 +2949,7 @@
         <v>25.0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I44" s="1">
         <v>100.0</v>
@@ -2985,7 +2985,7 @@
         <v>6.0</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45">
@@ -3005,7 +3005,7 @@
         <v>0.0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I45" s="1">
         <v>5.0</v>
@@ -3041,7 +3041,7 @@
         <v>6.0</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46">
@@ -3061,7 +3061,7 @@
         <v>3.0</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I46" s="1">
         <v>5.0</v>
@@ -3097,7 +3097,7 @@
         <v>6.0</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47">
@@ -3117,7 +3117,7 @@
         <v>6.0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I47" s="1">
         <v>5.0</v>
@@ -3153,7 +3153,7 @@
         <v>6.0</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
@@ -3173,7 +3173,7 @@
         <v>9.0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I48" s="1">
         <v>5.0</v>
@@ -3209,7 +3209,7 @@
         <v>6.0</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49">
@@ -3226,7 +3226,7 @@
         <v>0.0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I49" s="1">
         <v>5.0</v>
@@ -3263,12 +3263,12 @@
         <v>6.0</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
       <c r="E50" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F50" s="1">
         <v>8.0</v>
@@ -3277,7 +3277,7 @@
         <v>10.0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I50" s="1">
         <v>10.0</v>
@@ -3314,7 +3314,7 @@
         <v>6.0</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
@@ -3328,7 +3328,7 @@
         <v>15.0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I51" s="1">
         <v>7.5</v>
@@ -3365,7 +3365,7 @@
         <v>6.0</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -3379,7 +3379,7 @@
         <v>20.0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I52" s="1">
         <v>10.0</v>
@@ -3416,7 +3416,7 @@
         <v>6.0</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53">
@@ -3430,7 +3430,7 @@
         <v>25.0</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I53" s="1">
         <v>12.5</v>
@@ -3467,7 +3467,7 @@
         <v>6.0</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
@@ -3481,7 +3481,7 @@
         <v>30.0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I54" s="1">
         <v>15.0</v>
@@ -3518,7 +3518,7 @@
         <v>6.0</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55">
@@ -3532,7 +3532,7 @@
         <v>35.0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I55" s="1">
         <v>17.5</v>
@@ -3569,7 +3569,7 @@
         <v>6.0</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56">
@@ -3583,7 +3583,7 @@
         <v>40.0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I56" s="1">
         <v>20.0</v>
@@ -3620,7 +3620,7 @@
         <v>6.0</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="57">
@@ -3634,7 +3634,7 @@
         <v>45.0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I57" s="1">
         <v>22.5</v>
@@ -3671,7 +3671,7 @@
         <v>6.0</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
@@ -3685,7 +3685,7 @@
         <v>50.0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I58" s="1">
         <v>25.0</v>
@@ -3722,7 +3722,7 @@
         <v>6.0</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="59">
@@ -3739,7 +3739,7 @@
         <v>0.0</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I59" s="1">
         <v>5.0</v>
@@ -3775,12 +3775,12 @@
         <v>3.0</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60">
       <c r="E60" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F60" s="1">
         <v>8.0</v>
@@ -3789,7 +3789,7 @@
         <v>10.0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I60" s="1">
         <v>10.0</v>
@@ -3825,7 +3825,7 @@
         <v>3.0</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
@@ -3839,7 +3839,7 @@
         <v>15.0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I61" s="1">
         <v>7.5</v>
@@ -3875,7 +3875,7 @@
         <v>3.0</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62">
@@ -3889,7 +3889,7 @@
         <v>20.0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I62" s="1">
         <v>10.0</v>
@@ -3925,7 +3925,7 @@
         <v>3.0</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -3939,7 +3939,7 @@
         <v>25.0</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I63" s="1">
         <v>12.5</v>
@@ -3975,7 +3975,7 @@
         <v>3.0</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="64">
@@ -3989,7 +3989,7 @@
         <v>30.0</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I64" s="1">
         <v>15.0</v>
@@ -4025,7 +4025,7 @@
         <v>3.0</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="65">
@@ -4039,7 +4039,7 @@
         <v>35.0</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I65" s="1">
         <v>17.5</v>
@@ -4075,7 +4075,7 @@
         <v>3.0</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66">
@@ -4089,7 +4089,7 @@
         <v>40.0</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I66" s="1">
         <v>20.0</v>
@@ -4125,7 +4125,7 @@
         <v>3.0</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67">
@@ -4139,7 +4139,7 @@
         <v>45.0</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I67" s="1">
         <v>22.5</v>
@@ -4175,7 +4175,7 @@
         <v>3.0</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
@@ -4189,7 +4189,7 @@
         <v>50.0</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I68" s="1">
         <v>25.0</v>
@@ -4225,7 +4225,7 @@
         <v>3.0</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
@@ -4242,7 +4242,7 @@
         <v>0.0</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I69" s="1">
         <v>5.0</v>
@@ -4278,12 +4278,12 @@
         <v>18.0</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70">
       <c r="E70" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F70" s="1">
         <v>8.0</v>
@@ -4292,7 +4292,7 @@
         <v>10.0</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I70" s="1">
         <v>10.0</v>
@@ -4328,7 +4328,7 @@
         <v>18.0</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71">
@@ -4342,7 +4342,7 @@
         <v>15.0</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I71" s="1">
         <v>7.5</v>
@@ -4378,7 +4378,7 @@
         <v>18.0</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72">
@@ -4392,7 +4392,7 @@
         <v>20.0</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I72" s="1">
         <v>10.0</v>
@@ -4428,7 +4428,7 @@
         <v>18.0</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73">
@@ -4442,7 +4442,7 @@
         <v>25.0</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I73" s="1">
         <v>12.5</v>
@@ -4478,7 +4478,7 @@
         <v>18.0</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
@@ -4492,7 +4492,7 @@
         <v>30.0</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I74" s="1">
         <v>15.0</v>
@@ -4528,7 +4528,7 @@
         <v>18.0</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -4542,7 +4542,7 @@
         <v>35.0</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I75" s="1">
         <v>17.5</v>
@@ -4578,7 +4578,7 @@
         <v>18.0</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -4592,7 +4592,7 @@
         <v>40.0</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I76" s="1">
         <v>20.0</v>
@@ -4628,7 +4628,7 @@
         <v>18.0</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77">
@@ -4642,7 +4642,7 @@
         <v>45.0</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I77" s="1">
         <v>22.5</v>
@@ -4678,7 +4678,7 @@
         <v>18.0</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78">
@@ -4692,7 +4692,7 @@
         <v>50.0</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I78" s="1">
         <v>25.0</v>
@@ -4728,7 +4728,7 @@
         <v>18.0</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4753,26 +4753,26 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -5794,18 +5794,18 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" ht="15.0" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="15.0" customHeight="1">
@@ -5813,31 +5813,31 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="15.0" customHeight="1">
@@ -5850,7 +5850,7 @@
     </row>
     <row r="8" ht="15.0" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>34</v>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="9" ht="15.0" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>37</v>
@@ -5866,7 +5866,7 @@
     </row>
     <row r="10" ht="15.0" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>38</v>
@@ -5877,12 +5877,12 @@
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>42</v>
@@ -5906,7 +5906,7 @@
     </row>
     <row r="15" ht="15.0" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>45</v>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="16" ht="15.0" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>46</v>
@@ -5922,7 +5922,7 @@
     </row>
     <row r="17" ht="15.0" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>47</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>52</v>
@@ -5954,26 +5954,26 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1"/>
